--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
@@ -9,24 +9,35 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR estimates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Green items (no cost)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR Effort" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beyond the BRD - OOTB" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; DM scope" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$34</definedName>
+    <definedName name="DayRate">Assumptions!$B$6</definedName>
+    <definedName name="Accuracy">Assumptions!$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CR estimates'!$A$4:$R$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'CR estimates'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summary'!$A$4:$B$15</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$4:$B$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Assumptions'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Green items (no cost)'!$A$4:$H$27</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Green items (no cost)'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$T$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$I$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Integration &amp; DM scope'!$A$4:$F$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Integration &amp; DM scope'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Best practice (blue)'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Best practice (blue)'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$F$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'BRD items to deliver'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Assumptions'!$A$4:$B$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Assumptions'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,6 +57,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00004EA8"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00656565"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
@@ -53,17 +75,6 @@
       <name val="Arial"/>
       <color rgb="004B4B4B"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00004EA8"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00656565"/>
-      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -190,48 +201,48 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -349,7 +360,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -662,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E27"/>
+  <dimension ref="B4:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -819,65 +830,110 @@
     <row r="21">
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>One row per orange point of the FRS v1.2 (neither in the BRD nor out of the box), with the effort by activity</t>
+          <t>Totals of BRD-06 Renewal: change requests (orange), green, integration and best practice</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Totals of the change requests of BRD-06 Renewal</t>
+          <t>One row per orange point of the FRS v1.2 (not in the BRD, not in the iNXT BrokerVerse platform edition), effort by activity</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Assumptions of the estimate; the daily rate in B6 drives the cost columns</t>
+          <t>Points beyond the BRD that the iNXT BrokerVerse platform offers out of the box (green; no cost)</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Points beyond the BRD that the system offers out of the box (green in the FRS v1.2)</t>
+          <t>Points delivered in the Integration or Data Migration scope (grey label in the FRS): no CR cost here</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="B27" s="15" t="inlineStr">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Insurance-broking renewal practices not in the BRD, the FRS or the platform (Annex AP.2); recommendations</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>BRD requirements not fully in the platform edition: in-scope delivery work for planning, not change requests</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions of the estimate; the daily rate (DayRate, B6) drives the cost columns</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -890,6 +946,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -902,7 +961,83 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Complexity</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -912,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -960,30 +1095,26 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>CR No.</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Change request number of the register</t>
-        </is>
-      </c>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr"/>
       <c r="D5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr"/>
@@ -992,17 +1123,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>CR No.</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Where the orange point is stated</t>
+          <t>Change request number of the register</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr"/>
@@ -1010,58 +1141,62 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>BRD reference</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>BRD ID, or Not in BRD</t>
-        </is>
-      </c>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr"/>
       <c r="D8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr"/>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Where the orange point is stated</t>
+        </is>
+      </c>
       <c r="D9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Why needed</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr"/>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Not in BRD (what the BRD asks)</t>
+        </is>
+      </c>
       <c r="D10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Out-of-the-box status</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr"/>
@@ -1070,17 +1205,17 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Analysis and design (man-days)</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Estimate in man-days</t>
+          <t>Feature List vs OOTB, column OOTB platform</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr"/>
@@ -1088,17 +1223,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Back end (man-days)</t>
+          <t>OOTB evidence (iNXT BrokerVerse)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Estimate in man-days</t>
+          <t>Screen or module of the platform edition, or not found</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr"/>
@@ -1106,17 +1241,17 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Front end (man-days)</t>
+          <t>Prepared for BIBS?</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Estimate in man-days</t>
+          <t>Prepared for BIBS in this project; the effort is still the value of the change</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr"/>
@@ -1124,30 +1259,26 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Testing (man-days)</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Estimate in man-days</t>
-        </is>
-      </c>
+          <t>Why needed</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr"/>
       <c r="D15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Documentation and UAT support (man-days)</t>
+          <t>Analysis and design (man-days)</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1160,17 +1291,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Total man-days</t>
+          <t>Back end (man-days)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Sum of the activities</t>
+          <t>Estimate in man-days</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -1178,17 +1309,17 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Cost (at the rate of sheet Assumptions)</t>
+          <t>Front end (man-days)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Total x daily rate</t>
+          <t>Estimate in man-days</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr"/>
@@ -1196,104 +1327,120 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Complexity</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Low, Medium, High</t>
-        </is>
-      </c>
+          <t>Testing (man-days)</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Estimate in man-days</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>Documentation and UAT support (man-days)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Estimate in man-days</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr"/>
+          <t>Total man-days</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Sum of the activities</t>
+        </is>
+      </c>
       <c r="D21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr"/>
+          <t>Cost (man-days x DayRate)</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Total x the daily rate of sheet Assumptions</t>
+        </is>
+      </c>
       <c r="D22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Complexity</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr"/>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Low, Medium, High</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr"/>
@@ -1302,12 +1449,12 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
+          <t>CR Effort</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
           <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>Value</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
@@ -1316,7 +1463,7 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
@@ -1330,7 +1477,7 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -1344,7 +1491,7 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -1358,7 +1505,7 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
@@ -1372,7 +1519,7 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -1386,31 +1533,35 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Offered by the system out of the box</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr"/>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Feature List vs OOTB, column OOTB platform</t>
+        </is>
+      </c>
       <c r="D32" s="14" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>OOTB evidence (iNXT BrokerVerse)</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Candidate of the Change Request Register</t>
+          <t>Screen or module of the platform edition</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -1418,23 +1569,315 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Candidate of the Change Request Register</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Beyond the BRD - OOTB</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
           <t>Man-days</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Zero: out of the box</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr"/>
+      <c r="D35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>FR item</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr"/>
+      <c r="D37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>Interface or data</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr"/>
+      <c r="D39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Covered by</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr"/>
+      <c r="D40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr"/>
+      <c r="D41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr"/>
+      <c r="D42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr"/>
+      <c r="D44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr"/>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Excluded from the CR totals</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>Feature List ID</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr"/>
+      <c r="D47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Feature (BRD requirement)</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr"/>
+      <c r="D48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>BRD and FRS references</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr"/>
+      <c r="D49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>OOTB platform</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr"/>
+      <c r="D50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>What the platform offers</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr"/>
+      <c r="D51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr"/>
+      <c r="D52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr"/>
+      <c r="D53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr"/>
+      <c r="D54" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D34"/>
+  <autoFilter ref="A4:D54"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1455,253 +1898,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="36" customWidth="1" min="17" max="17"/>
-    <col width="44" customWidth="1" min="18" max="18"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>CR estimates</t>
+          <t>Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>One row per orange point of the FRS v1.2 (neither in the BRD nor out of the box), with the effort by activity</t>
+          <t>Totals of BRD-06 Renewal: change requests (orange), green, integration and best practice</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="20" t="n"/>
       <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="20" t="n"/>
-      <c r="K3" s="20" t="n"/>
-      <c r="L3" s="20" t="n"/>
-      <c r="M3" s="20" t="n"/>
-      <c r="N3" s="20" t="n"/>
-      <c r="O3" s="20" t="n"/>
-      <c r="P3" s="20" t="n"/>
-      <c r="Q3" s="20" t="n"/>
-      <c r="R3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>CR No.</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>FRS reference</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>BRD reference</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>Why needed</t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="inlineStr">
-        <is>
-          <t>Out-of-the-box status</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>Analysis and design (man-days)</t>
-        </is>
-      </c>
-      <c r="I4" s="21" t="inlineStr">
-        <is>
-          <t>Back end (man-days)</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t>Front end (man-days)</t>
-        </is>
-      </c>
-      <c r="K4" s="21" t="inlineStr">
-        <is>
-          <t>Testing (man-days)</t>
-        </is>
-      </c>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t>Documentation and UAT support (man-days)</t>
-        </is>
-      </c>
-      <c r="M4" s="21" t="inlineStr">
-        <is>
-          <t>Total man-days</t>
-        </is>
-      </c>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t>Cost (at the rate of sheet Assumptions)</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="inlineStr">
-        <is>
-          <t>Complexity</t>
-        </is>
-      </c>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="R4" s="21" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>CR-RN-024</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Accessibility conformance (WCAG 2.2 level AA) of the Renewal screens</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Annex AJ RN-NFR-16</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Programme register of non-functional requirements (NFR-ACC-01); market practice for bank systems</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>The BRD has no accessibility requirement; BDO's policies and the programme register expect screens usable with the keyboard and a screen reader, with sufficient contrast. A conformance claim needs a check of every Renewal screen and the corrections it finds.</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Partly: the screens have labelled fields, keyboard navigation and the programme colours; no conformance check of the Renewal screens against WCAG 2.2 AA and no conformance statement.</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" s="22" t="n">
+          <t>Change requests (orange points)</t>
+        </is>
+      </c>
+      <c r="B5" s="22">
+        <f>COUNTA('CR Effort'!A5:A21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Analysis and design (man-days)</t>
+        </is>
+      </c>
+      <c r="B6" s="22">
+        <f>SUM('CR Effort'!J5:J21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Back end (man-days)</t>
+        </is>
+      </c>
+      <c r="B7" s="22">
+        <f>SUM('CR Effort'!K5:K21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Front end (man-days)</t>
+        </is>
+      </c>
+      <c r="B8" s="22">
+        <f>SUM('CR Effort'!L5:L21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Testing (man-days)</t>
+        </is>
+      </c>
+      <c r="B9" s="22">
+        <f>SUM('CR Effort'!M5:M21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Documentation and UAT support (man-days)</t>
+        </is>
+      </c>
+      <c r="B10" s="22">
+        <f>SUM('CR Effort'!N5:N21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Total man-days of the change requests</t>
+        </is>
+      </c>
+      <c r="B11" s="22">
+        <f>SUM('CR Effort'!O5:O21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Low estimate (-20%)</t>
+        </is>
+      </c>
+      <c r="B12" s="22">
+        <f>B11*(1-Accuracy)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>High estimate (+20%)</t>
+        </is>
+      </c>
+      <c r="B13" s="22">
+        <f>B11*(1+Accuracy)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Cost at the daily rate</t>
+        </is>
+      </c>
+      <c r="B14" s="23">
+        <f>B11*DayRate</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Green points (beyond the BRD, out of the box, no cost)</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Integration and Data Migration scope (not change requests)</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="22">
-        <f>SUM(H5:L5)</f>
-        <v/>
-      </c>
-      <c r="N5" s="23">
-        <f>M5*Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="O5" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P5" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q5" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the accessibility standard (WCAG 2.2 AA or BDO's own); shared screen components of the programme</t>
-        </is>
-      </c>
-      <c r="R5" s="12" t="inlineStr">
-        <is>
-          <t>16 Renewal screens and their dialogs; corrections in the shared components benefit every module and are counted once here; no change to the business rules</t>
-        </is>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue), indicative man-days - not in the totals</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R5"/>
+  <autoFilter ref="A4:B17"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:R505">
+  <conditionalFormatting sqref="A5:B517">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation sqref="O5:O505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
-      <formula1>'Lists'!$A$2:$A$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="P5:P505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
-      <formula1>'Lists'!$B$2:$B$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1722,173 +2105,1717 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>CR Effort</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Totals of the change requests of BRD-06 Renewal</t>
+          <t>One row per orange point of the FRS v1.2 (not in the BRD, not in the iNXT BrokerVerse platform edition), effort by activity</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="20" t="n"/>
       <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="20" t="n"/>
+      <c r="K3" s="20" t="n"/>
+      <c r="L3" s="20" t="n"/>
+      <c r="M3" s="20" t="n"/>
+      <c r="N3" s="20" t="n"/>
+      <c r="O3" s="20" t="n"/>
+      <c r="P3" s="20" t="n"/>
+      <c r="Q3" s="20" t="n"/>
+      <c r="R3" s="20" t="n"/>
+      <c r="S3" s="20" t="n"/>
+      <c r="T3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>CR No.</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>OOTB evidence (iNXT BrokerVerse)</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS?</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Why needed</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>Analysis and design (man-days)</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>Back end (man-days)</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>Front end (man-days)</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>Testing (man-days)</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t>Documentation and UAT support (man-days)</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Total man-days</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>Cost (man-days x DayRate)</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="inlineStr">
+        <is>
+          <t>Complexity</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Change requests (orange points)</t>
-        </is>
-      </c>
-      <c r="B5" s="22">
-        <f>COUNTA('CR estimates'!A5:A5)</f>
+          <t>CR-RN-001</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Automatic assignment by team and sub-team (Annex F)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.010.01</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRD 1.005, 3.005 (the Team Lead assigns))</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>RNW-012: Partial</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Lead assignment rules only (Leads); renewal queue without automatic assignment (Operations &gt; Renewals &gt; Renewal Queue)</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; assignment and reassignment exist; automatic round-robin assignment of renewals by team and sub-team (Annex F) is the missing part in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="22">
+        <f>SUM(J5:N5)</f>
         <v/>
+      </c>
+      <c r="P5" s="23">
+        <f>O5*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Analysis and design (man-days)</t>
-        </is>
-      </c>
-      <c r="B6" s="22">
-        <f>SUM('CR estimates'!H5:H5)</f>
+          <t>CR-RN-002</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>New Business account from an accepted referral</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.011.03</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRD 1.006 (transfer of the account))</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>RNW-013: Not available</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>not found (no transfer or referral of renewals between units)</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; no transfer or referral of renewal accounts between units with acceptance in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O6" s="22">
+        <f>SUM(J6:N6)</f>
         <v/>
+      </c>
+      <c r="P6" s="23">
+        <f>O6*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Back end (man-days)</t>
-        </is>
-      </c>
-      <c r="B7" s="22">
-        <f>SUM('CR estimates'!I5:I5)</f>
+          <t>CR-RN-003</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Marketing dashboard metrics (budget, pipeline, closing ratio, top deals, persistency, product mix)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.002.02.01</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRD 1.009.7 (accounts per officer))</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>RNW-032; ACC-023: Partial</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Renewal Queue dashboard counters (total, due soon, at risk, grace); no budget, closing ratio, persistency or product mix</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; renewal dashboards are standard; the budget, closing ratio, top deals, persistency and product mix metrics of BDOI are not in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" s="22">
+        <f>SUM(J7:N7)</f>
         <v/>
+      </c>
+      <c r="P7" s="23">
+        <f>O7*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q7" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R7" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T7" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Front end (man-days)</t>
-        </is>
-      </c>
-      <c r="B8" s="22">
-        <f>SUM('CR estimates'!J5:J5)</f>
+          <t>CR-RN-004</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Processing dashboard cards and drill-downs</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.003.02</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRD 3.010.7)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>QPL-032: Partial</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Placement screens without processing cards or drill-downs</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; placement reports exist; the processing cards and drill-downs of BDOI are not in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" s="22">
+        <f>SUM(J8:N8)</f>
         <v/>
+      </c>
+      <c r="P8" s="23">
+        <f>O8*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R8" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T8" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Testing (man-days)</t>
-        </is>
-      </c>
-      <c r="B9" s="22">
-        <f>SUM('CR estimates'!K5:K5)</f>
+          <t>CR-RN-005</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Annual renewal budget maintenance, upload, inquiry and history</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.042.01</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRD 1.009.7 (dashboard))</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>ACC-023: Not available</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>not found (budget exists only on win-back campaigns)</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; no budget maintenance, upload, inquiry or history in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O9" s="22">
+        <f>SUM(J9:N9)</f>
         <v/>
+      </c>
+      <c r="P9" s="23">
+        <f>O9*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R9" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T9" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Documentation and UAT support (man-days)</t>
-        </is>
-      </c>
-      <c r="B10" s="22">
-        <f>SUM('CR estimates'!L5:L5)</f>
+          <t>CR-RN-006</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>KYC monitoring statuses, history and dashboard</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.039.02</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.028 (KYC flag))</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>RNW-010; CRM-010: Partial</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>AML: KYC refresh due list; no renewal KYC monitoring statuses or dashboard</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; a periodic KYC review list is standard; the KYC monitoring statuses, history and dashboard of Renewal are not in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" s="22">
+        <f>SUM(J10:N10)</f>
         <v/>
+      </c>
+      <c r="P10" s="23">
+        <f>O10*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T10" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Total man-days</t>
-        </is>
-      </c>
-      <c r="B11" s="22">
-        <f>SUM('CR estimates'!M5:M5)</f>
+          <t>CR-RN-008</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>CBG Motor automatic update (depreciation, BI / PD tiers, Auto Promo to Regular)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.009.01</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.039)</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS (Annexes D, E)</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Not in the feature list: BDOI-specific</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS (Annexes D, E) asks for it beyond the BRD; bDOI rules for CBG Motor renewals (Annexes D, E) in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O11" s="22">
+        <f>SUM(J11:N11)</f>
         <v/>
+      </c>
+      <c r="P11" s="23">
+        <f>O11*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R11" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T11" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Low estimate (-20%)</t>
-        </is>
-      </c>
-      <c r="B12" s="22">
-        <f>B11*(1-Assumptions!$B$7)</f>
+          <t>CR-RN-010</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Direct-to-Insurer Payment approval (blanket or Unit Head)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.014.05</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.040)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>POL-016; REM-019: Partial</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>not found (direct payment only in commission computation)</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; direct-payment accounts are standard; the blanket or Unit Head approval of the renewal is not in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N12" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O12" s="22">
+        <f>SUM(J12:N12)</f>
         <v/>
+      </c>
+      <c r="P12" s="23">
+        <f>O12*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q12" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R12" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T12" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>High estimate (+20%)</t>
-        </is>
-      </c>
-      <c r="B13" s="22">
-        <f>B11*(1+Assumptions!$B$7)</f>
+          <t>CR-RN-011</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Hold cover automation (CBG at 75 days, extensions, CBG Home on the 15th)</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.036.03</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.042)</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>RNW-028: Partial</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Cover notes of 30 days from an accepted quotation (Cover Notes); no automatic CBG requests, extensions or batches</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; cover notes of 30 days are standard; automatic CBG requests at 75 days, extensions and insurer batches are not in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="22">
+        <f>SUM(J13:N13)</f>
         <v/>
+      </c>
+      <c r="P13" s="23">
+        <f>O13*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q13" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R13" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T13" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Cost at the daily rate</t>
-        </is>
-      </c>
-      <c r="B14" s="23">
-        <f>B11*Assumptions!$B$6</f>
+          <t>CR-RN-014</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>E-policy batch processing (summary file and ZIP)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.033.01</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.040)</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>POL-009: Partial</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>E-policy issue for packages; no summary file and ZIP receipt or batch sending</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; protected e-policy dispatch is partly standard; the summary file and ZIP receipt, matching and batch sending are not in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O14" s="22">
+        <f>SUM(J14:N14)</f>
         <v/>
+      </c>
+      <c r="P14" s="23">
+        <f>O14*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q14" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R14" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T14" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Green points (beyond the BRD, out of the box, no cost)</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n">
-        <v>23</v>
+          <t>CR-RN-015</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Placement turnaround time (business days, With Issue, resolution date)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.29.05</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.040)</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>QPL-032 (no TAT feature): Not available</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; no placement turnaround time in business days with With Issue and resolution date in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O15" s="22">
+        <f>SUM(J15:N15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="23">
+        <f>O15*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q15" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R15" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T15" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-016</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Second approval after acceptance</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.26.01</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.040 (no delay))</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>RNW-016: Partial</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Maker-checker on other masters; no Submitted for Approval of an accepted renewal</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; maker-checker on renewal terms is standard; Submitted for Approval after acceptance is not in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O16" s="22">
+        <f>SUM(J16:N16)</f>
+        <v/>
+      </c>
+      <c r="P16" s="23">
+        <f>O16*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q16" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R16" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T16" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-017</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Nine insurer disposition values</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.013.02</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.035 (three outcomes))</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>RNW-021: BDOI-specific</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>not found (insurer responses not recorded as dispositions)</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; bDOI's nine insurer values and their mapping to the BRD outcomes in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O17" s="22">
+        <f>SUM(J17:N17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="23">
+        <f>O17*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q17" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R17" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T17" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-018</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate criteria per line and segment (Annex B)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.006.01</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.005)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>POL-003: Partial</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate checks on journals and data load; none per line and segment on renewals</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; duplicate account prevention is partly standard; criteria per line and segment (Annex B) are not in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O18" s="22">
+        <f>SUM(J18:N18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="23">
+        <f>O18*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q18" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R18" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T18" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-020</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Password convention of protected files</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.024.01</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.010 (encrypt and add password))</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>RNW-023; QPL-031: Not available</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>not found (documents sent as plain PDF)</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; documents are sent as plain PDF; no password convention in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O19" s="22">
+        <f>SUM(J19:N19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="23">
+        <f>O19*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q19" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R19" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T19" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-022</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>RMU Account Officer maintenance</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.041.01</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRRN.029)</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>RNW-009; INT-009: BDOI-specific</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks for it beyond the BRD; bank-specific RMU Account Officer codes in the iNXT BrokerVerse platform edition.</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L20" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M20" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O20" s="22">
+        <f>SUM(J20:N20)</f>
+        <v/>
+      </c>
+      <c r="P20" s="23">
+        <f>O20*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q20" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R20" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+        </is>
+      </c>
+      <c r="T20" s="12" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-024</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Accessibility conformance (WCAG 2.2 level AA) of the Renewal screens</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Annex AJ RN-NFR-16</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Programme register of non-functional requirements (NFR-ACC-01); market practice for bank systems</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>NFR-021: Partial</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Partial: ARIA labels on many screens; no WCAG 2.2 AA conformance check or statement</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>The BRD has no accessibility requirement; BDO's policies and the programme register expect screens usable with the keyboard and a screen reader, with sufficient contrast. A conformance claim needs a check of every Renewal screen and the corrections it finds.</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="M21" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" s="22">
+        <f>SUM(J21:N21)</f>
+        <v/>
+      </c>
+      <c r="P21" s="23">
+        <f>O21*DayRate</f>
+        <v/>
+      </c>
+      <c r="Q21" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R21" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the accessibility standard (WCAG 2.2 AA or BDO's own); shared screen components of the programme</t>
+        </is>
+      </c>
+      <c r="T21" s="12" t="inlineStr">
+        <is>
+          <t>16 Renewal screens and their dialogs; corrections in the shared components benefit every module and are counted once here; no change to the business rules</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B15"/>
+  <autoFilter ref="A4:T21"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:B515">
+  <conditionalFormatting sqref="A5:T521">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="Q5:Q521" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+      <formula1>'Lists'!$A$2:$A$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5:R521" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+      <formula1>'Lists'!$B$2:$B$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1909,115 +3836,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Assumptions of the estimate; the daily rate in B6 drives the cost columns</t>
+          <t>Points beyond the BRD that the iNXT BrokerVerse platform offers out of the box (green; no cost)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="20" t="n"/>
       <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>FR item</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>BRD (what it asks)</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>OOTB evidence (iNXT BrokerVerse)</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Man-days</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Hours per man-day</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>8</v>
+          <t>G-09</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.014.03</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Allocation to several insurers by percentage or amount</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>BRRN.040</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>QPL-016: Available</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Placement participants with insurer shares (Placement)</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-009</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Daily rate (fill in, currency of the contract)</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="n">
+          <t>G-19</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.022.01</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Renewal Advice per line; first and last notice set by the system</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>BRRN.010</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS (Annex L)</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>RNW-022: Available</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Renewal Batch with first, second and final notices from templates (Operations &gt; Renewals)</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-019</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Estimate accuracy (plus or minus)</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>The Renewal screens of the system (83 screen components, about 14,400 lines of screen code, 16 screens of Annex AA) and the rules of the change</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Not included</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Infrastructure, licences, BDOI's own testing time and travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Validity</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Until the FRS is signed; re-estimated in the impact assessment form of the Change Request Register</t>
-        </is>
+          <t>G-23</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.043.01</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Audit Logs menu with filters and export</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>BRRN.021</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>RNW-037: Available</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Audit trail module with filters (Administration &gt; Audit)</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-023</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B10"/>
+  <autoFilter ref="A4:I7"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:B510">
+  <conditionalFormatting sqref="A5:I507">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2042,30 +4087,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Green items (no cost)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Points beyond the BRD that the system offers out of the box (green in the FRS v1.2)</t>
+          <t>Points delivered in the Integration or Data Migration scope (grey label in the FRS): no CR cost here</t>
         </is>
       </c>
     </row>
@@ -2076,13 +4119,11 @@
       <c r="D3" s="20" t="n"/>
       <c r="E3" s="20" t="n"/>
       <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -2097,956 +4138,154 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>BRD (what it asks)</t>
+          <t>Interface or data</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Covered by</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>Offered by the system out of the box</t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="inlineStr">
-        <is>
-          <t>Register</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>Man-days</t>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>CR-RN-007</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>FRRN.010.01</t>
+          <t>FRRN.012.06</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Automatic assignment by team and sub-team (Annex F)</t>
+          <t>BDOFC and SOLD uploads and matching</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>BRD 1.005, 3.005 (the Team Lead assigns)</t>
+          <t>BDOFC and BDOSOLD reports of BDO systems</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS</t>
+          <t>Integration scope</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Automatic assignment of the market segments chosen to the Account Officer of the team with the fewest open accounts; a setting of Renewal Setup</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-001</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>0</v>
+          <t>Interface to an external system: delivered and costed in the Integration scope (Annex AH), not a change request</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>CR-RN-012</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>FRRN.011.03</t>
+          <t>FRRN.022.02</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>New Business account from an accepted referral</t>
+          <t>Delivery through CCM</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>BRD 1.006 (transfer of the account)</t>
+          <t>CCM of BDO (client communications)</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS</t>
+          <t>Integration scope</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Referral to another unit, accepted by the receiving unit, which opens the New Business account; transfer or referral is a setting</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-002</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>0</v>
+          <t>Interface to an external system: delivered and costed in the Integration scope (Annex AH), not a change request</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>CR-RN-013</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>FRRN.002.02.01</t>
+          <t>FRRN.29.03</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Marketing dashboard metrics (budget, pipeline, closing ratio, top deals, persistency, product mix)</t>
+          <t>MFT exchange with insurers</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>BRD 1.009.7 (accounts per officer)</t>
+          <t>MFT with the insurers</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS</t>
+          <t>Integration scope</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Renewal Dashboard with the budget, pipeline, closing ratio, top deals, persistency and product mix tiles and their drill-downs</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-003</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>0</v>
+          <t>Interface to an external system: delivered and costed in the Integration scope (Annex AH), not a change request</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>CR-RN-021</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>FRRN.003.02</t>
+          <t>FRRN.27.01</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Processing dashboard cards and drill-downs</t>
+          <t>Scheduled CLPC billing (CBG Home, FFY Motor) and the e-mail of Annex S</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>BRD 3.010.7</t>
+          <t>CLPC billing files to BDO CBG Loan Services (LMS)</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS</t>
+          <t>Integration scope</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Processing Dashboard with the placement, booking, policy and releasing cards and drill-downs</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-004</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>G-05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.042.01</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Annual renewal budget maintenance, upload, inquiry and history</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>BRD 1.009.7 (dashboard)</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Renewal Budget screen: maintenance with four eyes, upload, inquiry and history</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-005</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>G-06</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.039.02</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>KYC monitoring statuses, history and dashboard</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.028 (KYC flag)</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>KYC Monitoring screen with statuses, history and counts, and the daily KYC run</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-006</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>G-07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.012.06</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>BDOFC and SOLD uploads and matching</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.029</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Upload of the BDOFC and SOLD reports in the Upload Centre with matching on the PN and the sanitation rule</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-007</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>G-08</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.009.01</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>CBG Motor automatic update (depreciation, BI / PD tiers, Auto Promo to Regular)</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.039</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS (Annexes D, E)</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Automatic update of CBG Motor renewals with the depreciation and tier tables maintained by the Business Administrator</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-008</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>G-09</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.014.03</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Allocation to several insurers by percentage or amount</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.040</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Insurer allocation on the renewal account by percentage or amount</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-009</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>G-10</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.014.05</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Direct-to-Insurer Payment approval (blanket or Unit Head)</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.040</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Direct-to-Insurer Payment tag with blanket or Unit Head approval in the Approvals screen</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-010</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>G-11</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.036.03</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Hold cover automation (CBG at 75 days, extensions, CBG Home on the 15th)</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.042</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Hold Cover Requests with the automatic CBG requests, extensions and insurer batches</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-011</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>G-12</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.022.02</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Delivery through CCM</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.010 (sending)</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>CCM channel with delivery statuses in the Channel Monitor; the e-mail of the system as the fall-back. The connection details come from BDO ITG</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-012</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>G-13</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.29.03</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>MFT exchange with insurers</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.040</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>MFT inbox and per-insurer delivery of placement, hold cover and e-policy files</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-013</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>G-14</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.033.01</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>E-policy batch processing (summary file and ZIP)</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.040</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>E-policy screen: receipt of the summary file and ZIP, matching and batch sending</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-014</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>G-15</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.29.05</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Placement turnaround time (business days, With Issue, resolution date)</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.040</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Placement tracking with the TAT in business days, With Issue and resolution date</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-015</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>G-16</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.26.01</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Second approval after acceptance</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.040 (no delay)</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Submitted for Approval before placement, a setting (Annex AO C23)</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-016</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>G-17</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.013.02</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Nine insurer disposition values</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.035 (three outcomes)</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's nine values mapped to the three outcomes of the BRD in the insurer disposition list</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-017</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>G-18</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.006.01</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate criteria per line and segment (Annex B)</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.005</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate check of the sanitation with criteria per line and segment</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-018</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>G-19</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.022.01</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Renewal Advice per line; first and last notice set by the system</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.010</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS (Annex L)</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's Renewal Advice templates per line; notice set from the days before expiry (setting, Annex AO C13)</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-019</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>G-20</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.024.01</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Password convention of protected files</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.010 (encrypt and add password)</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's password convention, a setting (Annex AO C16)</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-020</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>G-21</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.27.01</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled CLPC billing (CBG Home, FFY Motor) and the e-mail of Annex S</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.040</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Billing Files screen and the scheduled billing runs</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-021</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>G-22</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.041.01</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>RMU Account Officer maintenance</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.029</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>RMU Officers screen</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-022</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>G-23</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.043.01</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Audit Logs menu with filters and export</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.021</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Audit Logs screen with filters and export</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-023</t>
-        </is>
-      </c>
-      <c r="H27" s="22" t="n">
-        <v>0</v>
+          <t>Interface to an external system: delivered and costed in the Integration scope (Annex AH), not a change request</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H27"/>
+  <autoFilter ref="A4:F8"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H527">
+  <conditionalFormatting sqref="A5:F508">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3071,62 +4310,1372 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>Complexity</t>
-        </is>
-      </c>
-      <c r="B1" s="26" t="inlineStr">
-        <is>
-          <t>Priority</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Insurance-broking renewal practices not in the BRD, the FRS or the platform (Annex AP.2); recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>BP-RN-01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Suitability review at renewal: the officer confirms the client's needs and covers are still adequate and records the advice given</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Fair treatment of clients and market-conduct expectations of the Insurance Commission for intermediaries; protects the broker against claims of poor advice</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>BP-RN-02</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Remarketing check: renewals above a premium threshold or with a large premium increase are quoted with at least one other insurer before the renewal is accepted</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>The broker acts for the client (Insurance Code); shows best terms were sought, especially on hardening rates</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>BP-RN-03</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Sum-insured adequacy prompt: property and motor renewals flag values not reviewed for two years or below an indexed value</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Avoids underinsurance and average at claim time, a common cause of client disputes</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>BP-RN-04</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Key-account renewal plan: accounts above a premium threshold get a stewardship review 120 days before expiry with claims, service and market summary</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Retention of the largest corporate accounts; market practice of corporate brokers</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="E8" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>BP-RN-05</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Remuneration disclosure on request: the Renewal Advice states that the commission or fee earned on the policy is disclosed on request</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Transparency expected of intermediaries by the Insurance Commission and good conduct practice</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="E9" s="22" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E9"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E509">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Suggested priority" error="Choose a value from the list (Suggested priority)." type="list">
+      <formula1>'Lists'!$B$2:$B$4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>BRD requirements not fully in the platform edition: in-scope delivery work for planning, not change requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Feature List ID</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Feature (BRD requirement)</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>BRD and FRS references</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>OOTB platform</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>What the platform offers</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>RNW-001</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Automatic extraction of renewal candidates at configurable lead days</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.030, BRRN.005 (Walkthrough Addendum p.8)</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>A daily job puts policies expiring within 90 days (one configurable value) into the renewal pipeline; there is no per-segment lead time and no extraction run log with its trigger.</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>RNW-002</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Expiring accounts list with multi-select filters, export and print</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.002-008, restating BRD 1.003 and 3.003</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Renewable policies can be listed by expiry window, insurer and product and a batch report exported to Excel or CSV; lists are paged (20, 50 or 100 rows) and BDOI's organisation filters (unit head, market segment, risk code) are not offered.</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>RNW-003</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Explicit initiation of renewal processing, single or in bulk by segment</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.021</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>A policy can be put into the pipeline on demand and batches can be created from criteria, but the pipeline job adds policies without a separate initiation step and there is no segment rule for bulk initiation.</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>RNW-004</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Go-live takeover of renewals and remapping of legacy packages</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.005, BRRN.020; BDOI decisions of 26-Sep-2026 (DMQ36-DMQ39)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>In-force policies loaded through the migration workbook enter the renewal pipeline like any other policy; there is no urgent flag for the go-live window and no remapping of legacy package codes.</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>BDOI-specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>RNW-005</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Sanitation, matching and eligibility checks on every candidate</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.020, BRRN.022 and Annex SC-01 to SC-13 (Walkthrough Addendum p.5, p.20-21)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>No configurable pre-renewal checks; the at-risk score uses claims and unpaid premium for retention, not for eligibility.</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>RNW-006</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Clean, Review and Exception classification with rule reference and controlled override</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.023 and Annex R23-01 to R23-05 (Walkthrough Addendum p.5-6, p.21)</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>At-risk bands rank renewals by retention risk; there is no eligibility classification with rule reference or override.</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>RNW-007</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Versioned decision matrix with straight-through disposition</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.031, BRRN.034 and Annex (Walkthrough Addendum p.9, p.23)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Renewal terms are prepared per policy by users; no decision matrix or automatic disposition.</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>RNW-008</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Non-renewable risk codes and Not-for-Renewal notice</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.009</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>A renewal can be lapsed with a reason; there is no master of non-renewable risk codes and no NFR letter.</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>RNW-009</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>LAMD paid-off and RMU loan reports matched to renewals</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.029, BRRN.039, BRRN.024 and Annex (Walkthrough Addendum p.6-8, p.23)</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>No loan-system feed or PN matching for renewals.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>BDOI-specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>RNW-010</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>KYC review due flag on renewal candidates</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.028 and Annex KYC-01 to KYC-06 (Walkthrough Addendum p.6-7, p.21-23)</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>KYC refresh dates and a due list exist per client in the AML area, and policy issue can be stopped pending EDD; the flag is not shown in the renewal queue.</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>RNW-011</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Renewal prepared from the latest endorsed policy</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.032; BRD 1.008.1.4</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>The renewal is pre-filled from the expiring policy as endorsed; a pending endorsement does not block the renewal.</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>RNW-012</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Assignment and re-assignment of renewal accounts to officers</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 1.005, BRRN.024</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Work can be reassigned from My Team by reporting line and renewals filtered by agent; no assignment tab for unassigned renewals.</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>RNW-013</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Transfer of renewal accounts between marketing units</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 1.006, 1.007, 2.005</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>No inter-unit transfer with acceptance.</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>RNW-014</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Officer disposition with remarks and re-opening</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 2.004, 2.006, 2.010, 3.004.5</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Renewal statuses, negotiation notes, lapse with reason and reinstatement exist; the BDOI disposition values and flags (Endorsed, Claims, lock) are not delivered.</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>RNW-016</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Team leader review, returns and controlled overrides</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 1.008, 1.011, 2.007, 3.008.2</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Renewal terms go to a checker who approves or rejects; there is no team-leader review queue, return flag or override of an outstanding-balance flag.</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>RNW-017</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Upload of offline dispositions keyed on a unique renewal reference</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.018, BRRN.022; BRD 3.004</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>No renewal reference or disposition upload; uploads exist for masters and go-live data only.</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>RNW-018</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Processing worklist and assignment to processing officers</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 3.005, 3.006, 4.003</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>The Renewal Queue and My Work list renewals with counters and filters; no assignment step for processing officers.</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>RNW-020</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Route renewals with material changes to the new business path</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.033, BRRN.038 (Walkthrough Addendum p.8-9)</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>A renewal can be made to follow the placement journey of its line; there is no tolerance-based routing or conversion tag.</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>RNW-021</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Insurer renewal-terms round trip by batch file</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 3.009, 4.007; BRRN.035 (Walkthrough Addendum p.9-11)</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Batches can be created by criteria and exported; there is no insurer extract layout and no upload of insurer responses.</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>RNW-023</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Encrypted, password-protected renewal letters</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 1.010.6-7, 2.009.6-7, 3.011.6-7</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Attachments are sent as plain PDF; no password protection.</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>RNW-024</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>No Advice, Non-Renewal and RA letter worklist with failure alerts</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.001 updated (Walkthrough Addendum p.15-16); BRRN.037</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Notice stages and wording are configurable and the outbox shows failed messages for retry; there are no eligibility rules for NAL or NRL.</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>RNW-025</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>NRNS identification and reminders on the effective expiry date</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.025, BRRN.037 and Annex R37-HC-01 to 12 (Walkthrough Addendum p.12, p.24-26)</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Unrenewed policies lapse after a 30-day grace period and reminders can be logged; there is no hold-cover-based effective expiry or NRNS routing.</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>RNW-026</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Client acceptance recorded by Marketing before placement and booking</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.035, BRRN.040 (Walkthrough Addendum p.4, p.9-11)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>The renewal quotation can be approved online by the client and the renewal completed by a user; acceptance method and evidence types are not recorded.</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>RNW-028</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Hold cover request and insurer confirmation for renewals</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.042 (Walkthrough Addendum p.14-15)</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Broker cover notes (30 days) can be issued from an accepted quotation or a placement slip; there is no hold-cover request to the insurer or confirmation record.</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>RNW-029</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Incentive eligibility of renewals after booking and full payment</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.041 (Walkthrough Addendum p.12-14)</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Incentive programmes for account executives exist; the timing rule (booking plus full payment) and re-evaluation on cancellation must be confirmed.</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>RNW-031</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Renewal of client-submitted policies handed over by Submitted Policies</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06; BRD-12 BRIDSP-22 to 26; cross-BRD decision D2</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>A policy recorded as issued by an insurer enters the renewal pipeline; there is no hand-over from a submitted-policy register.</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>RNW-033</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Renewal status report and centralised listings</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.019, BRRN.036 (Walkthrough Addendum p.11-12, p.24)</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Renewal Retention, Performance and the report builder cover status and outcome by product, agent and month; BDOI's twenty criteria and unit or segment filters are not all available.</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>RNW-035</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Renewal control reports (checks, decisions, LAMD, letters, insurer batches)</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.020, 023, 029, 031, 034; BRD 3.009, 4.007</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>No equivalent reports; they depend on the sanitation, decision and LAMD functions.</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>RNW-036</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Renewal rules, lists of values and letter templates maintained by the business</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 5.003, 5.005; BRRN.009, 023, 030, 034</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Renewal parameters and notice templates are business settings applied at once and audited; no effective dating or maker-checker on setting changes.</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F33"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:F533">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assumptions of the estimate; the daily rate (DayRate, B6) drives the cost columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Hours per man-day</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Daily rate (fill in, currency of the contract) - name DayRate</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Estimate accuracy (plus or minus) - name Accuracy</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Out of the box</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>The iNXT BrokerVerse platform edition (its code and manual), cross-checked with the Feature List vs OOTB workbook (column OOTB platform); the work prepared for BIBS in this project is not out of the box</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Effort for the missing part only, sized on the size of the Renewal work prepared for BIBS (about 55,700 lines of rules and services, 83 screen components)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Not included</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Integration and Data Migration scopes, infrastructure, licences, BDOI's own testing time and travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Until the FRS is signed; re-estimated in the impact assessment form of the Change Request Register</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:B11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:B511">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
@@ -21,11 +21,11 @@
   <definedNames>
     <definedName name="DayRate">Assumptions!$B$6</definedName>
     <definedName name="Accuracy">Assumptions!$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$T$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$T$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$I$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Integration &amp; DM scope'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Best practice (blue)'!$A$4:$E$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Best practice (blue)'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$F$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$H$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'BRD items to deliver'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Assumptions'!$A$4:$B$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Assumptions'!$4:$4</definedName>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -910,11 +910,11 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements not fully in the platform edition: in-scope delivery work for planning, not change requests</t>
+          <t>BRD requirements not fully in the platform edition: in-scope delivery work for planning, not change requests; the first rows were CR candidates and are in the BRD</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Feature List ID</t>
+          <t>ID (former CR / Feature List)</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>OOTB platform</t>
+          <t>BRD line (quoted)</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>What the platform offers</t>
+          <t>OOTB platform</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>What the platform offers / gap</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr"/>
@@ -1851,12 +1851,12 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr"/>
@@ -1865,19 +1865,51 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Planning man-days</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Delivery effort of the gap (not a change request)</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr"/>
+      <c r="D55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr"/>
-      <c r="D54" s="14" t="inlineStr"/>
+      <c r="C56" s="14" t="inlineStr"/>
+      <c r="D56" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D54"/>
+  <autoFilter ref="A4:D56"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1898,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -1942,7 +1974,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTA('CR Effort'!A5:A21)</f>
+        <f>COUNTA('CR Effort'!A5:A8)</f>
         <v/>
       </c>
     </row>
@@ -1953,7 +1985,7 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>SUM('CR Effort'!J5:J21)</f>
+        <f>SUM('CR Effort'!J5:J8)</f>
         <v/>
       </c>
     </row>
@@ -1964,7 +1996,7 @@
         </is>
       </c>
       <c r="B7" s="22">
-        <f>SUM('CR Effort'!K5:K21)</f>
+        <f>SUM('CR Effort'!K5:K8)</f>
         <v/>
       </c>
     </row>
@@ -1975,7 +2007,7 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>SUM('CR Effort'!L5:L21)</f>
+        <f>SUM('CR Effort'!L5:L8)</f>
         <v/>
       </c>
     </row>
@@ -1986,7 +2018,7 @@
         </is>
       </c>
       <c r="B9" s="22">
-        <f>SUM('CR Effort'!M5:M21)</f>
+        <f>SUM('CR Effort'!M5:M8)</f>
         <v/>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
         </is>
       </c>
       <c r="B10" s="22">
-        <f>SUM('CR Effort'!N5:N21)</f>
+        <f>SUM('CR Effort'!N5:N8)</f>
         <v/>
       </c>
     </row>
@@ -2008,7 +2040,7 @@
         </is>
       </c>
       <c r="B11" s="22">
-        <f>SUM('CR Effort'!O5:O21)</f>
+        <f>SUM('CR Effort'!O5:O8)</f>
         <v/>
       </c>
     </row>
@@ -2068,19 +2100,29 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
+          <t>BRD items to deliver that were CR candidates (in the BRD; planning man-days, not in the CR total)</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
           <t>Best practice (blue), indicative man-days - not in the totals</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B18" s="22" t="n">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B17"/>
+  <autoFilter ref="A4:B18"/>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:B517">
+  <conditionalFormatting sqref="A5:B518">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2105,7 +2147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2271,22 +2313,22 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>CR-RN-001</t>
+          <t>CR-RN-005</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Automatic assignment by team and sub-team (Annex F)</t>
+          <t>Annual renewal budget maintenance, upload, inquiry and history</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>FRRN.010.01</t>
+          <t>FRRN.042.01</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD (BRD 1.005, 3.005 (the Team Lead assigns))</t>
+          <t>Not in BRD (BRD 1.009.7 (dashboard))</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -2296,12 +2338,12 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>RNW-012: Partial</t>
+          <t>ACC-023: Not available</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Lead assignment rules only (Leads); renewal queue without automatic assignment (Operations &gt; Renewals &gt; Renewal Queue)</t>
+          <t>not found (budget exists only on win-back campaigns)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -2311,20 +2353,20 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS asks for it beyond the BRD; assignment and reassignment exist; automatic round-robin assignment of renewals by team and sub-team (Annex F) is the missing part in the iNXT BrokerVerse platform edition.</t>
+          <t>BDOI's FRS asks for it beyond the BRD; no budget maintenance, upload, inquiry or history in the iNXT BrokerVerse platform edition.</t>
         </is>
       </c>
       <c r="J5" s="22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="22" t="n">
         <v>2</v>
-      </c>
-      <c r="L5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="22" t="n">
-        <v>1.5</v>
       </c>
       <c r="N5" s="22" t="n">
         <v>0.5</v>
@@ -2339,12 +2381,12 @@
       </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="R5" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S5" s="12" t="inlineStr">
@@ -2361,37 +2403,37 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>CR-RN-002</t>
+          <t>CR-RN-008</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>New Business account from an accepted referral</t>
+          <t>CBG Motor rules of Annexes D and E only: depreciation schedule of the sum insured, BI / PD tier table and the Auto Promo to Regular conversion</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>FRRN.011.03</t>
+          <t>FRRN.009.01</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD (BRD 1.006 (transfer of the account))</t>
+          <t>Not in BRD (BRRN.039 asks for straight-through CBG Motor renewals, not these rules)</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS</t>
+          <t>BDOI's FRS (Annexes D, E)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>RNW-013: Not available</t>
+          <t>Not in the feature list: BDOI-specific</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>not found (no transfer or referral of renewals between units)</t>
+          <t>not found</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -2401,20 +2443,20 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS asks for it beyond the BRD; no transfer or referral of renewal accounts between units with acceptance in the iNXT BrokerVerse platform edition.</t>
+          <t>Only the BDOI product rules of Annexes D and E are beyond the BRD: the yearly depreciation of the CBG Motor sum insured, the BI / PD coverage tier table and the conversion of an Auto Promo policy to a Regular policy. The automatic update of the renewal account fields for straight-through CBG Motor renewals is the BRD (BRRN.039) and is a BRD item to deliver.</t>
         </is>
       </c>
       <c r="J6" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" s="22" t="n">
         <v>1.5</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="22" t="n">
-        <v>2</v>
       </c>
       <c r="N6" s="22" t="n">
         <v>0.5</v>
@@ -2429,12 +2471,12 @@
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="R6" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr">
@@ -2451,22 +2493,22 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>CR-RN-003</t>
+          <t>CR-RN-015</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Marketing dashboard metrics (budget, pipeline, closing ratio, top deals, persistency, product mix)</t>
+          <t>Placement turnaround time (business days, With Issue, resolution date)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>FRRN.002.02.01</t>
+          <t>FRRN.29.05</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD (BRD 1.009.7 (accounts per officer))</t>
+          <t>Not in BRD (BRRN.040)</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -2476,12 +2518,12 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>RNW-032; ACC-023: Partial</t>
+          <t>QPL-032 (no TAT feature): Not available</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Renewal Queue dashboard counters (total, due soon, at risk, grace); no budget, closing ratio, persistency or product mix</t>
+          <t>not found</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -2491,7 +2533,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS asks for it beyond the BRD; renewal dashboards are standard; the budget, closing ratio, top deals, persistency and product mix metrics of BDOI are not in the iNXT BrokerVerse platform edition.</t>
+          <t>BDOI's FRS asks for it beyond the BRD; no placement turnaround time in business days with With Issue and resolution date in the iNXT BrokerVerse platform edition.</t>
         </is>
       </c>
       <c r="J7" s="22" t="n">
@@ -2501,7 +2543,7 @@
         <v>3</v>
       </c>
       <c r="L7" s="22" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="22" t="n">
         <v>2</v>
@@ -2541,63 +2583,63 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>CR-RN-004</t>
+          <t>CR-RN-024</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Processing dashboard cards and drill-downs</t>
+          <t>Accessibility conformance (WCAG 2.2 level AA) of the Renewal screens</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>FRRN.003.02</t>
+          <t>Annex AJ RN-NFR-16</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD (BRD 3.010.7)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS</t>
+          <t>Programme register of non-functional requirements (NFR-ACC-01); market practice for bank systems</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>QPL-032: Partial</t>
+          <t>NFR-021: Partial</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Placement screens without processing cards or drill-downs</t>
+          <t>Partial: ARIA labels on many screens; no WCAG 2.2 AA conformance check or statement</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS asks for it beyond the BRD; placement reports exist; the processing cards and drill-downs of BDOI are not in the iNXT BrokerVerse platform edition.</t>
+          <t>The BRD has no accessibility requirement; BDO's policies and the programme register expect screens usable with the keyboard and a screen reader, with sufficient contrast. A conformance claim needs a check of every Renewal screen and the corrections it finds.</t>
         </is>
       </c>
       <c r="J8" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" s="22" t="n">
         <v>2</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <v>0.5</v>
       </c>
       <c r="O8" s="22">
         <f>SUM(J8:N8)</f>
@@ -2619,1200 +2661,30 @@
       </c>
       <c r="S8" s="12" t="inlineStr">
         <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
+          <t>BDOI confirms the accessibility standard (WCAG 2.2 AA or BDO's own); shared screen components of the programme</t>
         </is>
       </c>
       <c r="T8" s="12" t="inlineStr">
         <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-005</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Annual renewal budget maintenance, upload, inquiry and history</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.042.01</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRD 1.009.7 (dashboard))</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>ACC-023: Not available</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>not found (budget exists only on win-back campaigns)</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; no budget maintenance, upload, inquiry or history in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O9" s="22">
-        <f>SUM(J9:N9)</f>
-        <v/>
-      </c>
-      <c r="P9" s="23">
-        <f>O9*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q9" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R9" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S9" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T9" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-006</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>KYC monitoring statuses, history and dashboard</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.039.02</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.028 (KYC flag))</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>RNW-010; CRM-010: Partial</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>AML: KYC refresh due list; no renewal KYC monitoring statuses or dashboard</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; a periodic KYC review list is standard; the KYC monitoring statuses, history and dashboard of Renewal are not in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O10" s="22">
-        <f>SUM(J10:N10)</f>
-        <v/>
-      </c>
-      <c r="P10" s="23">
-        <f>O10*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q10" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R10" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S10" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-008</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>CBG Motor automatic update (depreciation, BI / PD tiers, Auto Promo to Regular)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.009.01</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.039)</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS (Annexes D, E)</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Not in the feature list: BDOI-specific</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS (Annexes D, E) asks for it beyond the BRD; bDOI rules for CBG Motor renewals (Annexes D, E) in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O11" s="22">
-        <f>SUM(J11:N11)</f>
-        <v/>
-      </c>
-      <c r="P11" s="23">
-        <f>O11*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q11" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R11" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="S11" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T11" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-010</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Direct-to-Insurer Payment approval (blanket or Unit Head)</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.014.05</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.040)</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>POL-016; REM-019: Partial</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>not found (direct payment only in commission computation)</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; direct-payment accounts are standard; the blanket or Unit Head approval of the renewal is not in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N12" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O12" s="22">
-        <f>SUM(J12:N12)</f>
-        <v/>
-      </c>
-      <c r="P12" s="23">
-        <f>O12*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q12" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R12" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S12" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T12" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-011</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Hold cover automation (CBG at 75 days, extensions, CBG Home on the 15th)</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.036.03</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.042)</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>RNW-028: Partial</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>Cover notes of 30 days from an accepted quotation (Cover Notes); no automatic CBG requests, extensions or batches</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; cover notes of 30 days are standard; automatic CBG requests at 75 days, extensions and insurer batches are not in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="22">
-        <f>SUM(J13:N13)</f>
-        <v/>
-      </c>
-      <c r="P13" s="23">
-        <f>O13*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q13" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R13" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="S13" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T13" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-014</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>E-policy batch processing (summary file and ZIP)</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.033.01</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.040)</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>POL-009: Partial</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>E-policy issue for packages; no summary file and ZIP receipt or batch sending</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; protected e-policy dispatch is partly standard; the summary file and ZIP receipt, matching and batch sending are not in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" s="22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N14" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O14" s="22">
-        <f>SUM(J14:N14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="23">
-        <f>O14*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q14" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R14" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S14" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T14" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-015</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Placement turnaround time (business days, With Issue, resolution date)</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.29.05</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.040)</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>QPL-032 (no TAT feature): Not available</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; no placement turnaround time in business days with With Issue and resolution date in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J15" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M15" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O15" s="22">
-        <f>SUM(J15:N15)</f>
-        <v/>
-      </c>
-      <c r="P15" s="23">
-        <f>O15*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q15" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R15" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S15" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T15" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-016</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Second approval after acceptance</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.26.01</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.040 (no delay))</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>RNW-016: Partial</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>Maker-checker on other masters; no Submitted for Approval of an accepted renewal</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; maker-checker on renewal terms is standard; Submitted for Approval after acceptance is not in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J16" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M16" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N16" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O16" s="22">
-        <f>SUM(J16:N16)</f>
-        <v/>
-      </c>
-      <c r="P16" s="23">
-        <f>O16*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q16" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R16" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S16" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T16" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-017</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Nine insurer disposition values</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.013.02</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.035 (three outcomes))</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>RNW-021: BDOI-specific</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>not found (insurer responses not recorded as dispositions)</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; bDOI's nine insurer values and their mapping to the BRD outcomes in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J17" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N17" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O17" s="22">
-        <f>SUM(J17:N17)</f>
-        <v/>
-      </c>
-      <c r="P17" s="23">
-        <f>O17*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q17" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R17" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S17" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T17" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-018</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate criteria per line and segment (Annex B)</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.006.01</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.005)</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>POL-003: Partial</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate checks on journals and data load; none per line and segment on renewals</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; duplicate account prevention is partly standard; criteria per line and segment (Annex B) are not in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M18" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N18" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O18" s="22">
-        <f>SUM(J18:N18)</f>
-        <v/>
-      </c>
-      <c r="P18" s="23">
-        <f>O18*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q18" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R18" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S18" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T18" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-020</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Password convention of protected files</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.024.01</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.010 (encrypt and add password))</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>RNW-023; QPL-031: Not available</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>not found (documents sent as plain PDF)</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; documents are sent as plain PDF; no password convention in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K19" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M19" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O19" s="22">
-        <f>SUM(J19:N19)</f>
-        <v/>
-      </c>
-      <c r="P19" s="23">
-        <f>O19*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q19" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R19" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="S19" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T19" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-022</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>RMU Account Officer maintenance</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.041.01</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRRN.029)</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>RNW-009; INT-009: BDOI-specific</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for it beyond the BRD; bank-specific RMU Account Officer codes in the iNXT BrokerVerse platform edition.</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K20" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L20" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M20" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O20" s="22">
-        <f>SUM(J20:N20)</f>
-        <v/>
-      </c>
-      <c r="P20" s="23">
-        <f>O20*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q20" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R20" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S20" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T20" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-024</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Accessibility conformance (WCAG 2.2 level AA) of the Renewal screens</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Annex AJ RN-NFR-16</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Programme register of non-functional requirements (NFR-ACC-01); market practice for bank systems</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>NFR-021: Partial</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>Partial: ARIA labels on many screens; no WCAG 2.2 AA conformance check or statement</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>The BRD has no accessibility requirement; BDO's policies and the programme register expect screens usable with the keyboard and a screen reader, with sufficient contrast. A conformance claim needs a check of every Renewal screen and the corrections it finds.</t>
-        </is>
-      </c>
-      <c r="J21" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" s="22">
-        <f>SUM(J21:N21)</f>
-        <v/>
-      </c>
-      <c r="P21" s="23">
-        <f>O21*DayRate</f>
-        <v/>
-      </c>
-      <c r="Q21" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R21" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S21" s="12" t="inlineStr">
-        <is>
-          <t>BDOI confirms the accessibility standard (WCAG 2.2 AA or BDO's own); shared screen components of the programme</t>
-        </is>
-      </c>
-      <c r="T21" s="12" t="inlineStr">
-        <is>
           <t>16 Renewal screens and their dialogs; corrections in the shared components benefit every module and are counted once here; no change to the business rules</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T21"/>
+  <autoFilter ref="A4:T8"/>
   <mergeCells count="1">
     <mergeCell ref="A2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:T521">
+  <conditionalFormatting sqref="A5:T508">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="Q5:Q521" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="Q5:Q508" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R521" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="R5:R508" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -4528,15 +3400,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4549,7 +3423,7 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>BRD requirements not fully in the platform edition: in-scope delivery work for planning, not change requests</t>
+          <t>BRD requirements not fully in the platform edition: in-scope delivery work for planning, not change requests; the first rows were CR candidates and are in the BRD</t>
         </is>
       </c>
     </row>
@@ -4560,11 +3434,13 @@
       <c r="D3" s="20" t="n"/>
       <c r="E3" s="20" t="n"/>
       <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Feature List ID</t>
+          <t>ID (former CR / Feature List)</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -4579,954 +3455,1698 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
+          <t>BRD line (quoted)</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
           <t>OOTB platform</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>What the platform offers</t>
-        </is>
-      </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
+          <t>What the platform offers / gap</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
           <t>Assessment</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Planning man-days</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>RNW-001</t>
+          <t>CR-RN-008 (BRD part)</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Automatic extraction of renewal candidates at configurable lead days</t>
+          <t>Automatic update of the CBG Motor renewal account fields (straight-through renewal)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.030, BRRN.005 (Walkthrough Addendum p.8)</t>
+          <t>BRRN.039; BRD 3.009.1.4.24 | FRRN.009.01</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>BRRN.039 "support LAMD-driven matching and categorization for CBG Motor and Fire renewals, including straight-through processing"; BRD 3.009.1.4.24 "Bodily Injury and Property Damage for Motor Accounts value"</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>A daily job puts policies expiring within 90 days (one configurable value) into the renewal pipeline; there is no per-segment lead time and no extraction run log with its trigger.</t>
+          <t>Not in the feature list: BDOI-specific</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
+          <t>Not available: the renewal account fields of FRRN.009.01 (risk code and rate, insurer, dates, OD / theft, BI and PD coverages and premiums, taxes, total premium) are not set by the system for a straight-through CBG Motor renewal.</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>PARTLY - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>RNW-002</t>
+          <t>CR-RN-001</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Expiring accounts list with multi-select filters, export and print</t>
+          <t>Automatic assignment by team and sub-team (Annex F)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.002-008, restating BRD 1.003 and 3.003</t>
+          <t>BRD 1.005.1, 3.005; BRRN.031 | FRRN.010.01</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>BRD 1.005.1 "a. Assign account to Marketing Account Officers (AO)"; BRD 3.005 (assignment to the Processing Officer); BRRN.031 "apply rule-based disposition automatically ... so that straight-through renewals proceed without manual effort"</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Renewable policies can be listed by expiry window, insurer and product and a batch report exported to Excel or CSV; lists are paged (20, 50 or 100 rows) and BDOI's organisation filters (unit head, market segment, risk code) are not offered.</t>
+          <t>RNW-012: Partial</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
+          <t>Partial: Assignment and reassignment exist; automatic round-robin assignment of renewals by team and sub-team (Annex F) is the missing part.</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>RNW-003</t>
+          <t>CR-RN-002</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Explicit initiation of renewal processing, single or in bulk by segment</t>
+          <t>New Business account from an accepted referral</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.021</t>
+          <t>BRD 1.006, 1.007.3; BRRN.033 | FRRN.011.03</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>BRD 1.006 "Transfer account to other units" (1.006.3 "Select from the drop-down the Marketing unit where the account will be transferred to", 1.006.4 "Submit transfer request"); BRD 1.007.3 "Accept transferred account/s"; BRRN.033 "allow renewal-identified accounts to follow the New Business flow"</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>A policy can be put into the pipeline on demand and batches can be created from criteria, but the pipeline job adds policies without a separate initiation step and there is no segment rule for bulk initiation.</t>
+          <t>RNW-013: Not available</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
+          <t>Not available: No transfer or referral of renewal accounts between units with acceptance.</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>RNW-004</t>
+          <t>CR-RN-003</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Go-live takeover of renewals and remapping of legacy packages</t>
+          <t>Marketing dashboard metrics (budget, pipeline, closing ratio, top deals, persistency, product mix)</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.005, BRRN.020; BDOI decisions of 26-Sep-2026 (DMQ36-DMQ39)</t>
+          <t>BRD 1.009.7; BRRN.021; BRD-00 BR-203 | FRRN.002.02.01</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>BRD 1.009.7 "g. View the assigned accounts per Marketing AO in a dashboard"; BRRN.021 "displayed on the screen/dashboard"; BRD-00 BR-203 "Dashboards and reports for real-time tracking and reporting"</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>In-force policies loaded through the migration workbook enter the renewal pipeline like any other policy; there is no urgent flag for the go-live window and no remapping of legacy package codes.</t>
+          <t>RNW-032; ACC-023: Partial</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>BDOI-specific</t>
-        </is>
+          <t>Partial: Renewal dashboards are standard; the budget, closing ratio, top deals, persistency and product mix metrics of BDOI are not.</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>RNW-005</t>
+          <t>CR-RN-004</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Sanitation, matching and eligibility checks on every candidate</t>
+          <t>Processing dashboard cards and drill-downs</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.020, BRRN.022 and Annex SC-01 to SC-13 (Walkthrough Addendum p.5, p.20-21)</t>
+          <t>BRD 3.010.7; BRD-00 BR-203 | FRRN.003.02</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BRD 3.010.7 "g. View the assigned accounts per Processing Officer in a dashboard"; BRD-00 BR-203 "Dashboards and reports for real-time tracking and reporting"</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>No configurable pre-renewal checks; the at-risk score uses claims and unpaid premium for retention, not for eligibility.</t>
+          <t>QPL-032: Partial</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
+          <t>Partial: Placement reports exist; the processing cards and drill-downs of BDOI are not.</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>RNW-006</t>
+          <t>CR-RN-006</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Clean, Review and Exception classification with rule reference and controlled override</t>
+          <t>KYC monitoring statuses, history and dashboard</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.023 and Annex R23-01 to R23-05 (Walkthrough Addendum p.5-6, p.21)</t>
+          <t>BRRN.028 | FRRN.039.02</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BRRN.028 "I want the system to identify and view accounts that are due or upcoming for KYC review, so that compliance monitoring and follow up can be performed without blocking or interrupting the renewal process"</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>At-risk bands rank renewals by retention risk; there is no eligibility classification with rule reference or override.</t>
+          <t>RNW-010; CRM-010: Partial</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
+          <t>Partial: A periodic KYC review list is standard; the KYC monitoring statuses, history and dashboard of Renewal are not.</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>RNW-007</t>
+          <t>CR-RN-010</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Versioned decision matrix with straight-through disposition</t>
+          <t>Direct-to-Insurer Payment approval (blanket or Unit Head)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.031, BRRN.034 and Annex (Walkthrough Addendum p.9, p.23)</t>
+          <t>BRD 2.004.4.4; BRD-00 BR-035 | FRRN.014.05</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BRD 2.004.4.4 "4. Direct to Insurer" (reason for non-renewal); BRD-00 BR-035 "allow user to tag of Direct Payment (DP)"</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Renewal terms are prepared per policy by users; no decision matrix or automatic disposition.</t>
+          <t>POL-016; REM-019: Partial</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
+          <t>Partial: Direct-payment accounts are standard; the blanket or Unit Head approval of the renewal is not.</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>RNW-008</t>
+          <t>CR-RN-011</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Non-renewable risk codes and Not-for-Renewal notice</t>
+          <t>Hold cover automation (CBG at 75 days, extensions, CBG Home on the 15th)</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.009</t>
+          <t>BRRN.042; BRD-00 BR-034 | FRRN.036.03</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BRRN.042 "I want to be able to send request for Hold Cover to insurer/s and to record the Hold Cover confirmation details received from the insurer"; BRD-00 BR-034 "the system sends a 30 days Hold Cover (HC) request to Insurer/s"</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>A renewal can be lapsed with a reason; there is no master of non-renewable risk codes and no NFR letter.</t>
+          <t>RNW-028: Partial</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
+          <t>Partial: Cover notes of 30 days are standard; automatic CBG requests at 75 days, extensions and insurer batches are not.</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>RNW-009</t>
+          <t>CR-RN-014</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>LAMD paid-off and RMU loan reports matched to renewals</t>
+          <t>E-policy batch processing (summary file and ZIP)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.029, BRRN.039, BRRN.024 and Annex (Walkthrough Addendum p.6-8, p.23)</t>
+          <t>BRD-00 BR-040 to BR-042; BRRN.040 | FRRN.033.01</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BRD-00 BR-040 "allow users to receive e-policy. (Individual or Batch)", BR-041 "send e-policy to client. (Individual or Batch)", BR-042 "updates client record to add e-policy and policy number. (Individual or Batch)"; BRRN.040 "the policy can be issued on time"</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>No loan-system feed or PN matching for renewals.</t>
+          <t>POL-009: Partial</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>BDOI-specific</t>
-        </is>
+          <t>Partial: Protected e-policy dispatch is partly standard; the summary file and ZIP receipt, matching and batch sending are not.</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>RNW-010</t>
+          <t>CR-RN-016</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>KYC review due flag on renewal candidates</t>
+          <t>Second approval after acceptance</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.028 and Annex KYC-01 to KYC-06 (Walkthrough Addendum p.6-7, p.21-23)</t>
+          <t>BRD 1.008.1, 1.009.3.2.10; BRRN.038 | FRRN.26.01</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>BRD 1.008.1 "Review and Post Disposition Accounts - a. Review Accounts"; BRD 1.009.3.2.10 "Total No. of Awaiting Marketing TL Approval (For Renewal)"; BRRN.038 "routing of renewal changes based on financial impact, ensuring proper approval"</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>KYC refresh dates and a due list exist per client in the AML area, and policy issue can be stopped pending EDD; the flag is not shown in the renewal queue.</t>
+          <t>RNW-016: Partial</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
+          <t>Partial: Maker-checker on renewal terms is standard; Submitted for Approval after acceptance is not.</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>RNW-011</t>
+          <t>CR-RN-017</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Renewal prepared from the latest endorsed policy</t>
+          <t>Nine insurer disposition values</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.032; BRD 1.008.1.4</t>
+          <t>BRRN.035 | FRRN.013.02</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>BRRN.035 "capture insurer responses (e.g., Approve/ Renew As-Is, Reject, Revise) and automatically apply them to the renewal workflow"</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>The renewal is pre-filled from the expiring policy as endorsed; a pending endorsement does not block the renewal.</t>
+          <t>RNW-021: BDOI-specific</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
+          <t>BDOI-specific: BDOI's nine insurer values and their mapping to the BRD outcomes.</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>RNW-012</t>
+          <t>CR-RN-018</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Assignment and re-assignment of renewal accounts to officers</t>
+          <t>Duplicate criteria per line and segment (Annex B)</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRD 1.005, BRRN.024</t>
+          <t>BRRN.005; BRD-00 BR-026 | FRRN.006.01</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>BRRN.005 negative scenario "List contains duplicate or irrelevant accounts"; BRD-00 BR-026 "sanitize ... based on configurable business rules ... such as duplicate detection"</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Work can be reassigned from My Team by reporting line and renewals filtered by agent; no assignment tab for unassigned renewals.</t>
+          <t>POL-003: Partial</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
+          <t>Partial: Duplicate account prevention is partly standard; criteria per line and segment (Annex B) are not.</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>RNW-013</t>
+          <t>CR-RN-020</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Transfer of renewal accounts between marketing units</t>
+          <t>Password convention of protected files</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRD 1.006, 1.007, 2.005</t>
+          <t>BRRN.010; BRD 1.010.7.1 | FRRN.024.01</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BRRN.010 "Send RA in batch, with encryption and password protection"; BRD 1.010.7.1 "1. Encrypt and add password prior to sending"</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>No inter-unit transfer with acceptance.</t>
+          <t>RNW-023; QPL-031: Not available</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
+          <t>Not available: Documents are sent as plain PDF; no password convention.</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>RNW-014</t>
+          <t>CR-RN-022</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Officer disposition with remarks and re-opening</t>
+          <t>RMU Account Officer maintenance</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRD 2.004, 2.006, 2.010, 3.004.5</t>
+          <t>BRD 2.004.4.1; BRRN.029 | FRRN.041.01</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>BRD 2.004.4.1 "1. Remedial Management Unit (RMU)"; BRRN.029 "ingest LAMD-provided reports and match paid-off loan records ... to determine renewal eligibility and proper routing"</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Renewal statuses, negotiation notes, lapse with reason and reinstatement exist; the BDOI disposition values and flags (Endorsed, Claims, lock) are not delivered.</t>
+          <t>RNW-009; INT-009: BDOI-specific</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
+          <t>BDOI-specific: Bank-specific RMU Account Officer codes.</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>IN BRD - was a CR candidate</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>RNW-016</t>
+          <t>RNW-001</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Team leader review, returns and controlled overrides</t>
+          <t>Automatic extraction of renewal candidates at configurable lead days</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRD 1.008, 1.011, 2.007, 3.008.2</t>
+          <t>BRD-06 BRRN.030, BRRN.005 (Walkthrough Addendum p.8)</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>Renewal terms go to a checker who approves or rejects; there is no team-leader review queue, return flag or override of an outstanding-balance flag.</t>
-        </is>
-      </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
+          <t>A daily job puts policies expiring within 90 days (one configurable value) into the renewal pipeline; there is no per-segment lead time and no extraction run log with its trigger.</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
           <t>Partial fit</t>
         </is>
       </c>
+      <c r="H19" s="22" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>RNW-017</t>
+          <t>RNW-002</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Upload of offline dispositions keyed on a unique renewal reference</t>
+          <t>Expiring accounts list with multi-select filters, export and print</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.018, BRRN.022; BRD 3.004</t>
+          <t>BRD-06 BRRN.002-008, restating BRD 1.003 and 3.003</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>No renewal reference or disposition upload; uploads exist for masters and go-live data only.</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
-      </c>
+          <t>Renewable policies can be listed by expiry window, insurer and product and a batch report exported to Excel or CSV; lists are paged (20, 50 or 100 rows) and BDOI's organisation filters (unit head, market segment, risk code) are not offered.</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>RNW-018</t>
+          <t>RNW-003</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Processing worklist and assignment to processing officers</t>
+          <t>Explicit initiation of renewal processing, single or in bulk by segment</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRD 3.005, 3.006, 4.003</t>
+          <t>BRD-06 BRRN.021</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>The Renewal Queue and My Work list renewals with counters and filters; no assignment step for processing officers.</t>
-        </is>
-      </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
+          <t>A policy can be put into the pipeline on demand and batches can be created from criteria, but the pipeline job adds policies without a separate initiation step and there is no segment rule for bulk initiation.</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
           <t>Partial fit</t>
         </is>
       </c>
+      <c r="H21" s="22" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>RNW-020</t>
+          <t>RNW-004</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Route renewals with material changes to the new business path</t>
+          <t>Go-live takeover of renewals and remapping of legacy packages</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.033, BRRN.038 (Walkthrough Addendum p.8-9)</t>
+          <t>BRD-06 BRRN.005, BRRN.020; BDOI decisions of 26-Sep-2026 (DMQ36-DMQ39)</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>A renewal can be made to follow the placement journey of its line; there is no tolerance-based routing or conversion tag.</t>
-        </is>
-      </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
-      </c>
+          <t>In-force policies loaded through the migration workbook enter the renewal pipeline like any other policy; there is no urgent flag for the go-live window and no remapping of legacy package codes.</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>BDOI-specific</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>RNW-021</t>
+          <t>RNW-005</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Insurer renewal-terms round trip by batch file</t>
+          <t>Sanitation, matching and eligibility checks on every candidate</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRD 3.009, 4.007; BRRN.035 (Walkthrough Addendum p.9-11)</t>
+          <t>BRD-06 BRRN.020, BRRN.022 and Annex SC-01 to SC-13 (Walkthrough Addendum p.5, p.20-21)</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Batches can be created by criteria and exported; there is no insurer extract layout and no upload of insurer responses.</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
-      </c>
+          <t>No configurable pre-renewal checks; the at-risk score uses claims and unpaid premium for retention, not for eligibility.</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>RNW-023</t>
+          <t>RNW-006</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Encrypted, password-protected renewal letters</t>
+          <t>Clean, Review and Exception classification with rule reference and controlled override</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRD 1.010.6-7, 2.009.6-7, 3.011.6-7</t>
+          <t>BRD-06 BRRN.023 and Annex R23-01 to R23-05 (Walkthrough Addendum p.5-6, p.21)</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Attachments are sent as plain PDF; no password protection.</t>
-        </is>
-      </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
+          <t>At-risk bands rank renewals by retention risk; there is no eligibility classification with rule reference or override.</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
           <t>Gap</t>
         </is>
       </c>
+      <c r="H24" s="22" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>RNW-024</t>
+          <t>RNW-007</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>No Advice, Non-Renewal and RA letter worklist with failure alerts</t>
+          <t>Versioned decision matrix with straight-through disposition</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.001 updated (Walkthrough Addendum p.15-16); BRRN.037</t>
+          <t>BRD-06 BRRN.031, BRRN.034 and Annex (Walkthrough Addendum p.9, p.23)</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Notice stages and wording are configurable and the outbox shows failed messages for retry; there are no eligibility rules for NAL or NRL.</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
-      </c>
+          <t>Renewal terms are prepared per policy by users; no decision matrix or automatic disposition.</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>RNW-025</t>
+          <t>RNW-008</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>NRNS identification and reminders on the effective expiry date</t>
+          <t>Non-renewable risk codes and Not-for-Renewal notice</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.025, BRRN.037 and Annex R37-HC-01 to 12 (Walkthrough Addendum p.12, p.24-26)</t>
+          <t>BRD-06 BRRN.009</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Unrenewed policies lapse after a 30-day grace period and reminders can be logged; there is no hold-cover-based effective expiry or NRNS routing.</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
-      </c>
+          <t>A renewal can be lapsed with a reason; there is no master of non-renewable risk codes and no NFR letter.</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>RNW-026</t>
+          <t>RNW-009</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Client acceptance recorded by Marketing before placement and booking</t>
+          <t>LAMD paid-off and RMU loan reports matched to renewals</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.035, BRRN.040 (Walkthrough Addendum p.4, p.9-11)</t>
+          <t>BRD-06 BRRN.029, BRRN.039, BRRN.024 and Annex (Walkthrough Addendum p.6-8, p.23)</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>The renewal quotation can be approved online by the client and the renewal completed by a user; acceptance method and evidence types are not recorded.</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
-      </c>
+          <t>No loan-system feed or PN matching for renewals.</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>BDOI-specific</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>RNW-028</t>
+          <t>RNW-010</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Hold cover request and insurer confirmation for renewals</t>
+          <t>KYC review due flag on renewal candidates</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.042 (Walkthrough Addendum p.14-15)</t>
+          <t>BRD-06 BRRN.028 and Annex KYC-01 to KYC-06 (Walkthrough Addendum p.6-7, p.21-23)</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>Broker cover notes (30 days) can be issued from an accepted quotation or a placement slip; there is no hold-cover request to the insurer or confirmation record.</t>
-        </is>
-      </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
+          <t>KYC refresh dates and a due list exist per client in the AML area, and policy issue can be stopped pending EDD; the flag is not shown in the renewal queue.</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
           <t>Partial fit</t>
         </is>
       </c>
+      <c r="H28" s="22" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>RNW-029</t>
+          <t>RNW-011</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Incentive eligibility of renewals after booking and full payment</t>
+          <t>Renewal prepared from the latest endorsed policy</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.041 (Walkthrough Addendum p.12-14)</t>
+          <t>BRD-06 BRRN.032; BRD 1.008.1.4</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Incentive programmes for account executives exist; the timing rule (booking plus full payment) and re-evaluation on cancellation must be confirmed.</t>
-        </is>
-      </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
+          <t>The renewal is pre-filled from the expiring policy as endorsed; a pending endorsement does not block the renewal.</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
           <t>Partial fit</t>
         </is>
       </c>
+      <c r="H29" s="22" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>RNW-031</t>
+          <t>RNW-012</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Renewal of client-submitted policies handed over by Submitted Policies</t>
+          <t>Assignment and re-assignment of renewal accounts to officers</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>BRD-06; BRD-12 BRIDSP-22 to 26; cross-BRD decision D2</t>
+          <t>BRD-06 BRD 1.005, BRRN.024</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>A policy recorded as issued by an insurer enters the renewal pipeline; there is no hand-over from a submitted-policy register.</t>
-        </is>
-      </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
+          <t>Work can be reassigned from My Team by reporting line and renewals filtered by agent; no assignment tab for unassigned renewals.</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
           <t>Partial fit</t>
         </is>
       </c>
+      <c r="H30" s="22" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>RNW-033</t>
+          <t>RNW-013</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Renewal status report and centralised listings</t>
+          <t>Transfer of renewal accounts between marketing units</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.019, BRRN.036 (Walkthrough Addendum p.11-12, p.24)</t>
+          <t>BRD-06 BRD 1.006, 1.007, 2.005</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Renewal Retention, Performance and the report builder cover status and outcome by product, agent and month; BDOI's twenty criteria and unit or segment filters are not all available.</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Partial fit</t>
-        </is>
-      </c>
+          <t>No inter-unit transfer with acceptance.</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>RNW-035</t>
+          <t>RNW-014</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Renewal control reports (checks, decisions, LAMD, letters, insurer batches)</t>
+          <t>Officer disposition with remarks and re-opening</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>BRD-06 BRRN.020, 023, 029, 031, 034; BRD 3.009, 4.007</t>
+          <t>BRD-06 BRD 2.004, 2.006, 2.010, 3.004.5</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>No equivalent reports; they depend on the sanitation, decision and LAMD functions.</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
-      </c>
+          <t>Renewal statuses, negotiation notes, lapse with reason and reinstatement exist; the BDOI disposition values and flags (Endorsed, Claims, lock) are not delivered.</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
+          <t>RNW-016</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Team leader review, returns and controlled overrides</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 1.008, 1.011, 2.007, 3.008.2</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Renewal terms go to a checker who approves or rejects; there is no team-leader review queue, return flag or override of an outstanding-balance flag.</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>RNW-017</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Upload of offline dispositions keyed on a unique renewal reference</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.018, BRRN.022; BRD 3.004</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>No renewal reference or disposition upload; uploads exist for masters and go-live data only.</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>RNW-018</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Processing worklist and assignment to processing officers</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 3.005, 3.006, 4.003</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>The Renewal Queue and My Work list renewals with counters and filters; no assignment step for processing officers.</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>RNW-020</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Route renewals with material changes to the new business path</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.033, BRRN.038 (Walkthrough Addendum p.8-9)</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>A renewal can be made to follow the placement journey of its line; there is no tolerance-based routing or conversion tag.</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>RNW-021</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Insurer renewal-terms round trip by batch file</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 3.009, 4.007; BRRN.035 (Walkthrough Addendum p.9-11)</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Batches can be created by criteria and exported; there is no insurer extract layout and no upload of insurer responses.</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>RNW-023</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Encrypted, password-protected renewal letters</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRD 1.010.6-7, 2.009.6-7, 3.011.6-7</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Attachments are sent as plain PDF; no password protection.</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>RNW-024</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>No Advice, Non-Renewal and RA letter worklist with failure alerts</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.001 updated (Walkthrough Addendum p.15-16); BRRN.037</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Notice stages and wording are configurable and the outbox shows failed messages for retry; there are no eligibility rules for NAL or NRL.</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>RNW-025</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>NRNS identification and reminders on the effective expiry date</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.025, BRRN.037 and Annex R37-HC-01 to 12 (Walkthrough Addendum p.12, p.24-26)</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Unrenewed policies lapse after a 30-day grace period and reminders can be logged; there is no hold-cover-based effective expiry or NRNS routing.</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>RNW-026</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Client acceptance recorded by Marketing before placement and booking</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.035, BRRN.040 (Walkthrough Addendum p.4, p.9-11)</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>The renewal quotation can be approved online by the client and the renewal completed by a user; acceptance method and evidence types are not recorded.</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>RNW-028</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Hold cover request and insurer confirmation for renewals</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.042 (Walkthrough Addendum p.14-15)</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Broker cover notes (30 days) can be issued from an accepted quotation or a placement slip; there is no hold-cover request to the insurer or confirmation record.</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>RNW-029</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Incentive eligibility of renewals after booking and full payment</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.041 (Walkthrough Addendum p.12-14)</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Incentive programmes for account executives exist; the timing rule (booking plus full payment) and re-evaluation on cancellation must be confirmed.</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>RNW-031</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Renewal of client-submitted policies handed over by Submitted Policies</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06; BRD-12 BRIDSP-22 to 26; cross-BRD decision D2</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>A policy recorded as issued by an insurer enters the renewal pipeline; there is no hand-over from a submitted-policy register.</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>RNW-033</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Renewal status report and centralised listings</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.019, BRRN.036 (Walkthrough Addendum p.11-12, p.24)</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Renewal Retention, Performance and the report builder cover status and outcome by product, agent and month; BDOI's twenty criteria and unit or segment filters are not all available.</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Partial fit</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>RNW-035</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Renewal control reports (checks, decisions, LAMD, letters, insurer batches)</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>BRD-06 BRRN.020, 023, 029, 031, 034; BRD 3.009, 4.007</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>No equivalent reports; they depend on the sanitation, decision and LAMD functions.</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
           <t>RNW-036</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Renewal rules, lists of values and letter templates maintained by the business</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>BRD-06 BRD 5.003, 5.005; BRRN.009, 023, 030, 034</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>Renewal parameters and notice templates are business settings applied at once and audited; no effective dating or maker-checker on setting changes.</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>Partial fit</t>
         </is>
       </c>
+      <c r="H47" s="22" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F33"/>
+  <autoFilter ref="A4:H47"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F533">
+  <conditionalFormatting sqref="A5:H547">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
@@ -12,32 +12,35 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR Effort" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beyond the BRD - OOTB" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; DM scope" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD covered - OOTB" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; DM scope" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="DayRate">Assumptions!$B$6</definedName>
     <definedName name="Accuracy">Assumptions!$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$64</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$T$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Integration &amp; DM scope'!$A$4:$F$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Integration &amp; DM scope'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Best practice (blue)'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Best practice (blue)'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$H$47</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'BRD items to deliver'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Assumptions'!$A$4:$B$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Assumptions'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD covered - OOTB'!$A$4:$H$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD covered - OOTB'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Integration &amp; DM scope'!$A$4:$F$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Integration &amp; DM scope'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Best practice (blue)'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Best practice (blue)'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BRD items to deliver'!$A$4:$H$47</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'BRD items to deliver'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Assumptions'!$A$4:$B$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Assumptions'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -360,7 +363,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -673,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E30"/>
+  <dimension ref="B4:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -839,7 +842,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -869,71 +872,86 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Points delivered in the Integration or Data Migration scope (grey label in the FRS): no CR cost here</t>
+          <t>BRD requirements (black in the FRS, in scope) that the iNXT BrokerVerse platform offers out of the box: no effort</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Insurance-broking renewal practices not in the BRD, the FRS or the platform (Annex AP.2); recommendations</t>
+          <t>Points delivered in the Integration or Data Migration scope (grey label in the FRS): no CR cost here</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements not fully in the platform edition: in-scope delivery work for planning, not change requests; the first rows were CR candidates and are in the BRD</t>
+          <t>Insurance-broking renewal practices not in the BRD, the FRS or the platform (Annex AP.2); recommendations</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="13" t="inlineStr">
         <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>BRD requirements not fully in the platform edition: in-scope delivery work for planning, not change requests; the first rows were CR candidates and are in the BRD</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Assumptions of the estimate; the daily rate (DayRate, B6) drives the cost columns</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D28" s="12" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="B30" s="15" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -949,6 +967,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -961,11 +980,156 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Assumptions of the estimate; the daily rate (DayRate, B6) drives the cost columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Hours per man-day</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Daily rate (fill in, currency of the contract) - name DayRate</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Estimate accuracy (plus or minus) - name Accuracy</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Out of the box</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>The iNXT BrokerVerse platform edition (its code and manual), cross-checked with the Feature List vs OOTB workbook (column OOTB platform); the work prepared for BIBS in this project is not out of the box</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Effort for the missing part only, sized on the size of the Renewal work prepared for BIBS (about 55,700 lines of rules and services, 83 screen components)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Not included</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Integration and Data Migration scopes, infrastructure, licences, BDOI's own testing time and travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Until the FRS is signed; re-estimated in the impact assessment form of the Change Request Register</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:B11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:B511">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1047,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1605,21 +1769,25 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Register</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr"/>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Former green number</t>
+        </is>
+      </c>
       <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
@@ -1633,7 +1801,7 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
@@ -1647,82 +1815,102 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>Interface or data</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr"/>
+          <t>BRD line (quoted)</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>BRD, BRD-00 or programme-wide NFR</t>
+        </is>
+      </c>
       <c r="D39" s="12" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Covered by</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr"/>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Feature List vs OOTB, column OOTB platform</t>
+        </is>
+      </c>
       <c r="D40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr"/>
+          <t>OOTB evidence (iNXT BrokerVerse)</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Screen or module of the platform edition</t>
+        </is>
+      </c>
       <c r="D41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr"/>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Closed candidate of the Change Request Register</t>
+        </is>
+      </c>
       <c r="D42" s="14" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Practice</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr"/>
+          <t>Man-days</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Zero: BRD requirement offered out of the box</t>
+        </is>
+      </c>
       <c r="D43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Why it matters for a broker</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr"/>
@@ -1731,48 +1919,40 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Suggested priority</t>
+          <t>FR item</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+      <c r="D45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Indicative man-days</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>Excluded from the CR totals</t>
-        </is>
-      </c>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr"/>
       <c r="D46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>ID (former CR / Feature List)</t>
+          <t>Interface or data</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr"/>
@@ -1781,12 +1961,12 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>Feature (BRD requirement)</t>
+          <t>Covered by</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr"/>
@@ -1795,12 +1975,12 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>BRD and FRS references</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr"/>
@@ -1809,12 +1989,12 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>BRD line (quoted)</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr"/>
@@ -1823,12 +2003,12 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>OOTB platform</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr"/>
@@ -1837,12 +2017,12 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>What the platform offers / gap</t>
+          <t>Why it matters for a broker</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr"/>
@@ -1851,31 +2031,35 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>Suggested priority</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr"/>
-      <c r="D53" s="12" t="inlineStr"/>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>Planning man-days</t>
+          <t>Indicative man-days</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Delivery effort of the gap (not a change request)</t>
+          <t>Excluded from the CR totals</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -1883,12 +2067,12 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>ID (former CR / Feature List)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr"/>
@@ -1897,19 +2081,135 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Feature (BRD requirement)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr"/>
       <c r="D56" s="14" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>BRD and FRS references</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr"/>
+      <c r="D57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>BRD line (quoted)</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr"/>
+      <c r="D58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>OOTB platform</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr"/>
+      <c r="D59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>What the platform offers / gap</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr"/>
+      <c r="D60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr"/>
+      <c r="D61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>Planning man-days</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Delivery effort of the gap (not a change request)</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr"/>
+      <c r="D63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr"/>
+      <c r="D64" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D56"/>
+  <autoFilter ref="A4:D64"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1930,7 +2230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -2084,45 +2384,55 @@
         </is>
       </c>
       <c r="B15" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Integration and Data Migration scope (not change requests)</t>
+          <t>BRD requirements offered out of the box (black; in scope; no effort)</t>
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver that were CR candidates (in the BRD; planning man-days, not in the CR total)</t>
+          <t>Integration and Data Migration scope (not change requests)</t>
         </is>
       </c>
       <c r="B17" s="22" t="n">
-        <v>107.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>BRD items to deliver that were CR candidates (in the BRD; planning man-days, not in the CR total)</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
           <t>Best practice (blue), indicative man-days - not in the totals</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B19" s="22" t="n">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B18"/>
+  <autoFilter ref="A4:B19"/>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:B518">
+  <conditionalFormatting sqref="A5:B519">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2708,7 +3018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2839,102 +3149,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>G-19</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.022.01</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Renewal Advice per line; first and last notice set by the system</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.010</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS (Annex L)</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>RNW-022: Available</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Renewal Batch with first, second and final notices from templates (Operations &gt; Renewals)</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-019</t>
-        </is>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>G-23</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>FRRN.043.01</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Audit Logs menu with filters and export</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>BRRN.021</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>RNW-037: Available</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Audit trail module with filters (Administration &gt; Audit)</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>CR-RN-023</t>
-        </is>
-      </c>
-      <c r="I7" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:I7"/>
+  <autoFilter ref="A4:I5"/>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:I507">
+  <conditionalFormatting sqref="A5:I505">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2959,6 +3179,195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>BRD covered - OOTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>BRD requirements (black in the FRS, in scope) that the iNXT BrokerVerse platform offers out of the box: no effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>FR item</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>BRD line (quoted)</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>OOTB evidence (iNXT BrokerVerse)</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Man-days</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>G-19</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.022.01</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Renewal Advice per line; first and last notice set by the system</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>BRRN.010 "Generate Renewal Advice (RA) ... Identify if RA is for first or second notice"; acceptance: "The system generates Renewal Advice (RA) for each selected account, using the latest BDOI-approved RA template" and "Each RA clearly displays whether it is a First Notice or Second Notice"</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>RNW-022: Available</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Renewal Batch with first, second and final notices from templates (Operations &gt; Renewals)</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-019</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>G-23</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>FRRN.043.01</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Audit Logs menu with filters and export</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>BRD-00 User &amp; Data Management, User access and record: "audit logs are viewable/exportable"; programme NFR 4.05 (Collections, Claims, ReInsurance addenda) "Audit logs should be exportable"; Renewal BRD BRRN.010 "All actions ... are logged with user ID, timestamp, and affected account(s)"</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>RNW-037: Available</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Audit trail module with filters (Administration &gt; Audit)</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>CR-RN-023</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H6"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:H506">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3176,7 +3585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3394,7 +3803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5163,149 +5572,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>Assumptions of the estimate; the daily rate (DayRate, B6) drives the cost columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="20" t="n"/>
-      <c r="B3" s="20" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Hours per man-day</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Daily rate (fill in, currency of the contract) - name DayRate</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Estimate accuracy (plus or minus) - name Accuracy</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Out of the box</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>The iNXT BrokerVerse platform edition (its code and manual), cross-checked with the Feature List vs OOTB workbook (column OOTB platform); the work prepared for BIBS in this project is not out of the box</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Effort for the missing part only, sized on the size of the Renewal work prepared for BIBS (about 55,700 lines of rules and services, 83 screen components)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Not included</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Integration and Data Migration scopes, infrastructure, licences, BDOI's own testing time and travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Validity</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Until the FRS is signed; re-estimated in the impact assessment form of the Change Request Register</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:B11"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:B511">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
@@ -22,11 +22,11 @@
   <definedNames>
     <definedName name="DayRate">Assumptions!$B$6</definedName>
     <definedName name="Accuracy">Assumptions!$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$T$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$S$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -686,13 +686,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -721,6 +724,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -793,6 +797,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -950,6 +955,8 @@
         <v>7</v>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="15" t="inlineStr">
         <is>
@@ -1065,7 +1072,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>The iNXT BrokerVerse platform edition (its code and manual), cross-checked with the Feature List vs OOTB workbook (column OOTB platform); the work prepared for BIBS in this project is not out of the box</t>
+          <t>The iNXT BrokerVerse platform edition (its code and manual), cross-checked with the Feature List vs OOTB workbook (column OOTB platform)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1084,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Effort for the missing part only, sized on the size of the Renewal work prepared for BIBS (about 55,700 lines of rules and services, 83 screen components)</t>
+          <t>Effort for the missing part only, sized against the iNXT BrokerVerse platform edition and the requirements of the BRD and of BDOI's FRS</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1234,6 +1241,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1410,14 +1418,10 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is still the value of the change</t>
-        </is>
-      </c>
+          <t>Why needed</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr"/>
       <c r="D14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1428,10 +1432,14 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Why needed</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr"/>
+          <t>Analysis and design (man-days)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Estimate in man-days</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1442,7 +1450,7 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Analysis and design (man-days)</t>
+          <t>Back end (man-days)</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1460,7 +1468,7 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Back end (man-days)</t>
+          <t>Front end (man-days)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -1478,7 +1486,7 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Front end (man-days)</t>
+          <t>Testing (man-days)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1496,7 +1504,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Testing (man-days)</t>
+          <t>Documentation and UAT support (man-days)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1514,12 +1522,12 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Documentation and UAT support (man-days)</t>
+          <t>Total man-days</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Estimate in man-days</t>
+          <t>Sum of the activities</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr"/>
@@ -1532,12 +1540,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Total man-days</t>
+          <t>Cost (man-days x DayRate)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Sum of the activities</t>
+          <t>Total x the daily rate of sheet Assumptions</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
@@ -1550,15 +1558,15 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Cost (man-days x DayRate)</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>Total x the daily rate of sheet Assumptions</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr"/>
+          <t>Complexity</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Low, Medium, High</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -1568,13 +1576,13 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Complexity</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr"/>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Low, Medium, High</t>
+          <t>High, Medium, Low</t>
         </is>
       </c>
     </row>
@@ -1586,15 +1594,11 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+      <c r="D24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -1604,7 +1608,7 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr"/>
@@ -1613,12 +1617,12 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>CR Effort</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
@@ -1632,7 +1636,7 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>FR item</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr"/>
@@ -1646,7 +1650,7 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>FR item</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr"/>
@@ -1660,7 +1664,7 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>BRD (what it asks)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr"/>
@@ -1674,7 +1678,7 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>BRD (what it asks)</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr"/>
@@ -1688,10 +1692,14 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr"/>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Feature List vs OOTB, column OOTB platform</t>
+        </is>
+      </c>
       <c r="D31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1702,12 +1710,12 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence (iNXT BrokerVerse)</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Feature List vs OOTB, column OOTB platform</t>
+          <t>Screen or module of the platform edition</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr"/>
@@ -1720,12 +1728,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>OOTB evidence (iNXT BrokerVerse)</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Screen or module of the platform edition</t>
+          <t>Candidate of the Change Request Register</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -1738,12 +1746,12 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Man-days</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Candidate of the Change Request Register</t>
+          <t>Zero: out of the box</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr"/>
@@ -1751,17 +1759,17 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Beyond the BRD - OOTB</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Zero: out of the box</t>
+          <t>Former green number</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr"/>
@@ -1774,14 +1782,10 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>Former green number</t>
-        </is>
-      </c>
+          <t>FR item</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr"/>
       <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1792,7 +1796,7 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>FR item</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr"/>
@@ -1806,10 +1810,14 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr"/>
+          <t>BRD line (quoted)</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>BRD, BRD-00 or programme-wide NFR</t>
+        </is>
+      </c>
       <c r="D38" s="14" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1820,12 +1828,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>BRD line (quoted)</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>BRD, BRD-00 or programme-wide NFR</t>
+          <t>Feature List vs OOTB, column OOTB platform</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -1838,12 +1846,12 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence (iNXT BrokerVerse)</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Feature List vs OOTB, column OOTB platform</t>
+          <t>Screen or module of the platform edition</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -1856,12 +1864,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>OOTB evidence (iNXT BrokerVerse)</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Screen or module of the platform edition</t>
+          <t>Closed candidate of the Change Request Register</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -1874,12 +1882,12 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Man-days</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Closed candidate of the Change Request Register</t>
+          <t>Zero: BRD requirement offered out of the box</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -1887,19 +1895,15 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>BRD covered - OOTB</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Man-days</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Zero: BRD requirement offered out of the box</t>
-        </is>
-      </c>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr"/>
       <c r="D43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1910,7 +1914,7 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>FR item</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr"/>
@@ -1924,7 +1928,7 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>FR item</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr"/>
@@ -1938,7 +1942,7 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Interface or data</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr"/>
@@ -1952,7 +1956,7 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Interface or data</t>
+          <t>Covered by</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr"/>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>Covered by</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr"/>
@@ -1975,12 +1979,12 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr"/>
@@ -1994,7 +1998,7 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr"/>
@@ -2008,7 +2012,7 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>Why it matters for a broker</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr"/>
@@ -2022,11 +2026,15 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>Why it matters for a broker</t>
+          <t>Suggested priority</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr"/>
-      <c r="D52" s="14" t="inlineStr"/>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -2036,32 +2044,28 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Suggested priority</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="inlineStr"/>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Excluded from the CR totals</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>Indicative man-days</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>Excluded from the CR totals</t>
-        </is>
-      </c>
+          <t>ID (former CR / Feature List)</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr"/>
       <c r="D54" s="14" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2072,7 +2076,7 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>ID (former CR / Feature List)</t>
+          <t>Feature (BRD requirement)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr"/>
@@ -2086,7 +2090,7 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>Feature (BRD requirement)</t>
+          <t>BRD and FRS references</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr"/>
@@ -2100,7 +2104,7 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>BRD and FRS references</t>
+          <t>BRD line (quoted)</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr"/>
@@ -2114,7 +2118,7 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>BRD line (quoted)</t>
+          <t>OOTB platform</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr"/>
@@ -2128,7 +2132,7 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>OOTB platform</t>
+          <t>What the platform offers / gap</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr"/>
@@ -2142,7 +2146,7 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>What the platform offers / gap</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr"/>
@@ -2156,28 +2160,28 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr"/>
+          <t>Planning man-days</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Delivery effort of the gap (not a change request)</t>
+        </is>
+      </c>
       <c r="D61" s="12" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>Planning man-days</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="inlineStr">
-        <is>
-          <t>Delivery effort of the gap (not a change request)</t>
-        </is>
-      </c>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr"/>
       <c r="D62" s="14" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2188,28 +2192,14 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr"/>
       <c r="D63" s="12" t="inlineStr"/>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="B64" s="18" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr"/>
-      <c r="D64" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D64"/>
+  <autoFilter ref="A4:D63"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2285,54 +2275,54 @@
         </is>
       </c>
       <c r="B6" s="22">
+        <f>SUM('CR Effort'!I5:I8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Back end (man-days)</t>
+        </is>
+      </c>
+      <c r="B7" s="22">
         <f>SUM('CR Effort'!J5:J8)</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Back end (man-days)</t>
-        </is>
-      </c>
-      <c r="B7" s="22">
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Front end (man-days)</t>
+        </is>
+      </c>
+      <c r="B8" s="22">
         <f>SUM('CR Effort'!K5:K8)</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Front end (man-days)</t>
-        </is>
-      </c>
-      <c r="B8" s="22">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Testing (man-days)</t>
+        </is>
+      </c>
+      <c r="B9" s="22">
         <f>SUM('CR Effort'!L5:L8)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Testing (man-days)</t>
-        </is>
-      </c>
-      <c r="B9" s="22">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Documentation and UAT support (man-days)</t>
+        </is>
+      </c>
+      <c r="B10" s="22">
         <f>SUM('CR Effort'!M5:M8)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Documentation and UAT support (man-days)</t>
-        </is>
-      </c>
-      <c r="B10" s="22">
-        <f>SUM('CR Effort'!N5:N8)</f>
-        <v/>
-      </c>
-    </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
@@ -2340,7 +2330,7 @@
         </is>
       </c>
       <c r="B11" s="22">
-        <f>SUM('CR Effort'!O5:O8)</f>
+        <f>SUM('CR Effort'!N5:N8)</f>
         <v/>
       </c>
     </row>
@@ -2457,7 +2447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2467,19 +2457,18 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2516,7 +2505,6 @@
       <c r="Q3" s="20" t="n"/>
       <c r="R3" s="20" t="n"/>
       <c r="S3" s="20" t="n"/>
-      <c r="T3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
@@ -2556,65 +2544,60 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
+          <t>Why needed</t>
         </is>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>Why needed</t>
+          <t>Analysis and design (man-days)</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t>Analysis and design (man-days)</t>
+          <t>Back end (man-days)</t>
         </is>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
-          <t>Back end (man-days)</t>
+          <t>Front end (man-days)</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t>Front end (man-days)</t>
+          <t>Testing (man-days)</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr">
         <is>
-          <t>Testing (man-days)</t>
+          <t>Documentation and UAT support (man-days)</t>
         </is>
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t>Documentation and UAT support (man-days)</t>
+          <t>Total man-days</t>
         </is>
       </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
-          <t>Total man-days</t>
+          <t>Cost (man-days x DayRate)</t>
         </is>
       </c>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t>Cost (man-days x DayRate)</t>
+          <t>Complexity</t>
         </is>
       </c>
       <c r="Q4" s="21" t="inlineStr">
         <is>
-          <t>Complexity</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="S4" s="21" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="T4" s="21" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
@@ -2658,37 +2641,37 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
           <t>BDOI's FRS asks for it beyond the BRD; no budget maintenance, upload, inquiry or history in the iNXT BrokerVerse platform edition.</t>
         </is>
       </c>
+      <c r="I5" s="22" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J5" s="22" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="K5" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="O5" s="22">
-        <f>SUM(J5:N5)</f>
+      <c r="N5" s="22">
+        <f>SUM(I5:M5)</f>
         <v/>
       </c>
-      <c r="P5" s="23">
-        <f>O5*DayRate</f>
+      <c r="O5" s="23">
+        <f>N5*DayRate</f>
         <v/>
       </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2696,17 +2679,12 @@
       </c>
       <c r="R5" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
         </is>
       </c>
       <c r="S5" s="12" t="inlineStr">
         <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T5" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+          <t>The effort is the value of the change for the missing part</t>
         </is>
       </c>
     </row>
@@ -2748,37 +2726,37 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
           <t>Only the BDOI product rules of Annexes D and E are beyond the BRD: the yearly depreciation of the CBG Motor sum insured, the BI / PD coverage tier table and the conversion of an Auto Promo policy to a Regular policy. The automatic update of the renewal account fields for straight-through CBG Motor renewals is the BRD (BRRN.039) and is a BRD item to deliver.</t>
         </is>
       </c>
+      <c r="I6" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="J6" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" s="22" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M6" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="M6" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N6" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O6" s="22">
-        <f>SUM(J6:N6)</f>
+      <c r="N6" s="22">
+        <f>SUM(I6:M6)</f>
         <v/>
       </c>
-      <c r="P6" s="23">
-        <f>O6*DayRate</f>
+      <c r="O6" s="23">
+        <f>N6*DayRate</f>
         <v/>
       </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>High</t>
@@ -2786,17 +2764,12 @@
       </c>
       <c r="R6" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T6" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+          <t>The effort is the value of the change for the missing part</t>
         </is>
       </c>
     </row>
@@ -2838,37 +2811,37 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
           <t>BDOI's FRS asks for it beyond the BRD; no placement turnaround time in business days with With Issue and resolution date in the iNXT BrokerVerse platform edition.</t>
         </is>
       </c>
+      <c r="I7" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="J7" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" s="22" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L7" s="22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M7" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="O7" s="22">
-        <f>SUM(J7:N7)</f>
+      <c r="N7" s="22">
+        <f>SUM(I7:M7)</f>
         <v/>
       </c>
-      <c r="P7" s="23">
-        <f>O7*DayRate</f>
+      <c r="O7" s="23">
+        <f>N7*DayRate</f>
         <v/>
       </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2876,17 +2849,12 @@
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>BDOI confirms the point is in scope (Change Request Register)</t>
         </is>
       </c>
       <c r="S7" s="12" t="inlineStr">
         <is>
-          <t>BDOI confirms the point is in scope (Change Request Register)</t>
-        </is>
-      </c>
-      <c r="T7" s="12" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS in this project; the effort is the value of the change for the missing part</t>
+          <t>The effort is the value of the change for the missing part</t>
         </is>
       </c>
     </row>
@@ -2928,37 +2896,37 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
           <t>The BRD has no accessibility requirement; BDO's policies and the programme register expect screens usable with the keyboard and a screen reader, with sufficient contrast. A conformance claim needs a check of every Renewal screen and the corrections it finds.</t>
         </is>
       </c>
+      <c r="I8" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="J8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" s="22">
-        <f>SUM(J8:N8)</f>
+      <c r="N8" s="22">
+        <f>SUM(I8:M8)</f>
         <v/>
       </c>
-      <c r="P8" s="23">
-        <f>O8*DayRate</f>
+      <c r="O8" s="23">
+        <f>N8*DayRate</f>
         <v/>
       </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2966,35 +2934,30 @@
       </c>
       <c r="R8" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>BDOI confirms the accessibility standard (WCAG 2.2 AA or BDO's own); shared screen components of the programme</t>
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr">
         <is>
-          <t>BDOI confirms the accessibility standard (WCAG 2.2 AA or BDO's own); shared screen components of the programme</t>
-        </is>
-      </c>
-      <c r="T8" s="12" t="inlineStr">
-        <is>
           <t>16 Renewal screens and their dialogs; corrections in the shared components benefit every module and are counted once here; no change to the business rules</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T8"/>
+  <autoFilter ref="A4:S8"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:T508">
+  <conditionalFormatting sqref="A5:S508">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="Q5:Q508" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="P5:P508" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R508" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="Q5:Q508" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
@@ -49,7 +49,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,6 +132,11 @@
       <b val="1"/>
       <color rgb="004B4B4B"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
     </font>
   </fonts>
   <fills count="4">
@@ -238,7 +243,7 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -980,7 +985,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1126,7 +1131,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1202,7 +1207,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2204,7 +2209,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2373,7 +2378,7 @@
           <t>Green points (beyond the BRD, out of the box, no cost)</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2431,7 +2436,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2965,7 +2970,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3126,7 +3131,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3315,7 +3320,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3538,7 +3543,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3756,7 +3761,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5527,7 +5532,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_CR_BRD-06_Effort_Estimate_v1.0.xlsx
@@ -2968,7 +2968,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
